--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY142"/>
+  <dimension ref="A1:AY144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6321,10 +6321,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135152655</v>
+        <v>135471439</v>
       </c>
       <c r="B51" t="n">
-        <v>99219</v>
+        <v>98219</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6332,45 +6332,41 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219847</v>
+        <v>219815</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>492133</v>
+        <v>491957</v>
       </c>
       <c r="R51" t="n">
-        <v>7024725</v>
+        <v>7024690</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6394,12 +6390,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6412,27 +6408,22 @@
       <c r="AG51" t="b">
         <v>0</v>
       </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Rikkärr med barrträd</t>
-        </is>
-      </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135152656</v>
+        <v>135152655</v>
       </c>
       <c r="B52" t="n">
         <v>99219</v>
@@ -6475,10 +6466,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>492109</v>
+        <v>492133</v>
       </c>
       <c r="R52" t="n">
-        <v>7024713</v>
+        <v>7024725</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6511,11 +6502,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6548,7 +6534,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135152657</v>
+        <v>135152656</v>
       </c>
       <c r="B53" t="n">
         <v>99219</v>
@@ -6591,10 +6577,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>492126</v>
+        <v>492109</v>
       </c>
       <c r="R53" t="n">
-        <v>7024712</v>
+        <v>7024713</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6627,6 +6613,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6659,7 +6650,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135152658</v>
+        <v>135152657</v>
       </c>
       <c r="B54" t="n">
         <v>99219</v>
@@ -6702,10 +6693,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>492125</v>
+        <v>492126</v>
       </c>
       <c r="R54" t="n">
-        <v>7024725</v>
+        <v>7024712</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6738,11 +6729,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Gott om blommande tvåblad på denna fyndplats i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6775,7 +6761,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135152659</v>
+        <v>135152658</v>
       </c>
       <c r="B55" t="n">
         <v>99219</v>
@@ -6818,10 +6804,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>492115</v>
+        <v>492125</v>
       </c>
       <c r="R55" t="n">
-        <v>7024713</v>
+        <v>7024725</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6858,7 +6844,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Blommande tvåblad i ett fuktstråk med rikkärr.</t>
+          <t>Gott om blommande tvåblad på denna fyndplats i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6873,7 +6859,7 @@
       </c>
       <c r="AH55" t="inlineStr">
         <is>
-          <t>Rikkärr med vide</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6891,10 +6877,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135152736</v>
+        <v>135152659</v>
       </c>
       <c r="B56" t="n">
-        <v>99533</v>
+        <v>99219</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6902,28 +6888,28 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L56" t="inlineStr"/>
@@ -6934,10 +6920,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>492090</v>
+        <v>492115</v>
       </c>
       <c r="R56" t="n">
-        <v>7024764</v>
+        <v>7024713</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6972,6 +6958,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Blommande tvåblad i ett fuktstråk med rikkärr.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6984,7 +6975,7 @@
       </c>
       <c r="AH56" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med vide</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7002,10 +6993,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135152786</v>
+        <v>135152736</v>
       </c>
       <c r="B57" t="n">
-        <v>108205</v>
+        <v>99533</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7013,21 +7004,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220083</v>
+        <v>219880</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7045,10 +7036,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>492020</v>
+        <v>492090</v>
       </c>
       <c r="R57" t="n">
-        <v>7024753</v>
+        <v>7024764</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7113,7 +7104,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135152787</v>
+        <v>135152786</v>
       </c>
       <c r="B58" t="n">
         <v>108205</v>
@@ -7156,10 +7147,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>492029</v>
+        <v>492020</v>
       </c>
       <c r="R58" t="n">
-        <v>7024730</v>
+        <v>7024753</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7224,7 +7215,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135152788</v>
+        <v>135152787</v>
       </c>
       <c r="B59" t="n">
         <v>108205</v>
@@ -7267,10 +7258,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>491922</v>
+        <v>492029</v>
       </c>
       <c r="R59" t="n">
-        <v>7024675</v>
+        <v>7024730</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7335,7 +7326,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135152789</v>
+        <v>135152788</v>
       </c>
       <c r="B60" t="n">
         <v>108205</v>
@@ -7378,10 +7369,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>492046</v>
+        <v>491922</v>
       </c>
       <c r="R60" t="n">
-        <v>7024702</v>
+        <v>7024675</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7446,10 +7437,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135152730</v>
+        <v>135152789</v>
       </c>
       <c r="B61" t="n">
-        <v>108274</v>
+        <v>108205</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7457,28 +7448,28 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -7489,10 +7480,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>492122</v>
+        <v>492046</v>
       </c>
       <c r="R61" t="n">
-        <v>7024715</v>
+        <v>7024702</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7557,7 +7548,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135152731</v>
+        <v>135152730</v>
       </c>
       <c r="B62" t="n">
         <v>108274</v>
@@ -7589,7 +7580,7 @@
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -7600,10 +7591,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>492054</v>
+        <v>492122</v>
       </c>
       <c r="R62" t="n">
-        <v>7024760</v>
+        <v>7024715</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7668,7 +7659,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135152732</v>
+        <v>135152731</v>
       </c>
       <c r="B63" t="n">
         <v>108274</v>
@@ -7700,7 +7691,7 @@
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -7711,10 +7702,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492006</v>
+        <v>492054</v>
       </c>
       <c r="R63" t="n">
-        <v>7024744</v>
+        <v>7024760</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7779,7 +7770,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135152733</v>
+        <v>135152732</v>
       </c>
       <c r="B64" t="n">
         <v>108274</v>
@@ -7809,7 +7800,11 @@
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -7818,10 +7813,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492028</v>
+        <v>492006</v>
       </c>
       <c r="R64" t="n">
-        <v>7024713</v>
+        <v>7024744</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7886,7 +7881,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135152734</v>
+        <v>135152733</v>
       </c>
       <c r="B65" t="n">
         <v>108274</v>
@@ -7916,11 +7911,7 @@
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -7929,10 +7920,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>491910</v>
+        <v>492028</v>
       </c>
       <c r="R65" t="n">
-        <v>7024671</v>
+        <v>7024713</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7997,7 +7988,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135152735</v>
+        <v>135152734</v>
       </c>
       <c r="B66" t="n">
         <v>108274</v>
@@ -8040,10 +8031,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>491933</v>
+        <v>491910</v>
       </c>
       <c r="R66" t="n">
-        <v>7024735</v>
+        <v>7024671</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8108,10 +8099,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135152723</v>
+        <v>135152735</v>
       </c>
       <c r="B67" t="n">
-        <v>111153</v>
+        <v>108274</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8119,28 +8110,28 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220240</v>
+        <v>220102</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Linnea</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Linnaea borealis</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L67" t="inlineStr"/>
@@ -8151,10 +8142,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492012</v>
+        <v>491933</v>
       </c>
       <c r="R67" t="n">
-        <v>7024773</v>
+        <v>7024735</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8219,7 +8210,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135152724</v>
+        <v>135152723</v>
       </c>
       <c r="B68" t="n">
         <v>111153</v>
@@ -8262,10 +8253,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492071</v>
+        <v>492012</v>
       </c>
       <c r="R68" t="n">
-        <v>7024721</v>
+        <v>7024773</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8330,7 +8321,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135152726</v>
+        <v>135152724</v>
       </c>
       <c r="B69" t="n">
         <v>111153</v>
@@ -8373,10 +8364,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>491927</v>
+        <v>492071</v>
       </c>
       <c r="R69" t="n">
-        <v>7024670</v>
+        <v>7024721</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8441,7 +8432,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135152727</v>
+        <v>135152726</v>
       </c>
       <c r="B70" t="n">
         <v>111153</v>
@@ -8484,10 +8475,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492058</v>
+        <v>491927</v>
       </c>
       <c r="R70" t="n">
-        <v>7024686</v>
+        <v>7024670</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8552,7 +8543,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>135152728</v>
+        <v>135152727</v>
       </c>
       <c r="B71" t="n">
         <v>111153</v>
@@ -8595,10 +8586,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492099</v>
+        <v>492058</v>
       </c>
       <c r="R71" t="n">
-        <v>7024679</v>
+        <v>7024686</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8663,10 +8654,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>135152646</v>
+        <v>135152728</v>
       </c>
       <c r="B72" t="n">
-        <v>106309</v>
+        <v>111153</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8674,28 +8665,28 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>221725</v>
+        <v>220240</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Linnea</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Linnaea borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L72" t="inlineStr"/>
@@ -8706,10 +8697,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>491996</v>
+        <v>492099</v>
       </c>
       <c r="R72" t="n">
-        <v>7024788</v>
+        <v>7024679</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8742,11 +8733,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8779,10 +8765,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>135152674</v>
+        <v>135152646</v>
       </c>
       <c r="B73" t="n">
-        <v>99217</v>
+        <v>106309</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8790,28 +8776,28 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
@@ -8822,10 +8808,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>491994</v>
+        <v>491996</v>
       </c>
       <c r="R73" t="n">
-        <v>7024761</v>
+        <v>7024788</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8858,6 +8844,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8890,10 +8881,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>135152791</v>
+        <v>135152674</v>
       </c>
       <c r="B74" t="n">
-        <v>101403</v>
+        <v>99217</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8901,21 +8892,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8933,10 +8924,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492096</v>
+        <v>491994</v>
       </c>
       <c r="R74" t="n">
-        <v>7024659</v>
+        <v>7024761</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9001,7 +8992,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>135152792</v>
+        <v>135152791</v>
       </c>
       <c r="B75" t="n">
         <v>101403</v>
@@ -9044,10 +9035,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>492058</v>
+        <v>492096</v>
       </c>
       <c r="R75" t="n">
-        <v>7024648</v>
+        <v>7024659</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9112,7 +9103,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>135152793</v>
+        <v>135152792</v>
       </c>
       <c r="B76" t="n">
         <v>101403</v>
@@ -9155,10 +9146,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>492036</v>
+        <v>492058</v>
       </c>
       <c r="R76" t="n">
-        <v>7024661</v>
+        <v>7024648</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9223,7 +9214,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>135152794</v>
+        <v>135152793</v>
       </c>
       <c r="B77" t="n">
         <v>101403</v>
@@ -9266,10 +9257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>492083</v>
+        <v>492036</v>
       </c>
       <c r="R77" t="n">
-        <v>7024682</v>
+        <v>7024661</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9334,7 +9325,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>135152795</v>
+        <v>135152794</v>
       </c>
       <c r="B78" t="n">
         <v>101403</v>
@@ -9377,10 +9368,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>492072</v>
+        <v>492083</v>
       </c>
       <c r="R78" t="n">
-        <v>7024744</v>
+        <v>7024682</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9445,7 +9436,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>135152796</v>
+        <v>135152795</v>
       </c>
       <c r="B79" t="n">
         <v>101403</v>
@@ -9488,10 +9479,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>492083</v>
+        <v>492072</v>
       </c>
       <c r="R79" t="n">
-        <v>7024768</v>
+        <v>7024744</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9556,7 +9547,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135152797</v>
+        <v>135152796</v>
       </c>
       <c r="B80" t="n">
         <v>101403</v>
@@ -9599,10 +9590,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492050</v>
+        <v>492083</v>
       </c>
       <c r="R80" t="n">
-        <v>7024793</v>
+        <v>7024768</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9667,7 +9658,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135152798</v>
+        <v>135152797</v>
       </c>
       <c r="B81" t="n">
         <v>101403</v>
@@ -9710,10 +9701,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>491976</v>
+        <v>492050</v>
       </c>
       <c r="R81" t="n">
-        <v>7024781</v>
+        <v>7024793</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9778,7 +9769,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>135152799</v>
+        <v>135152798</v>
       </c>
       <c r="B82" t="n">
         <v>101403</v>
@@ -9821,10 +9812,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>491940</v>
+        <v>491976</v>
       </c>
       <c r="R82" t="n">
-        <v>7024802</v>
+        <v>7024781</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9889,7 +9880,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>135152800</v>
+        <v>135152799</v>
       </c>
       <c r="B83" t="n">
         <v>101403</v>
@@ -9932,10 +9923,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>491935</v>
+        <v>491940</v>
       </c>
       <c r="R83" t="n">
-        <v>7024778</v>
+        <v>7024802</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10000,7 +9991,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>135152801</v>
+        <v>135152800</v>
       </c>
       <c r="B84" t="n">
         <v>101403</v>
@@ -10043,10 +10034,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>491932</v>
+        <v>491935</v>
       </c>
       <c r="R84" t="n">
-        <v>7024802</v>
+        <v>7024778</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10111,7 +10102,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135152802</v>
+        <v>135152801</v>
       </c>
       <c r="B85" t="n">
         <v>101403</v>
@@ -10154,10 +10145,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>491980</v>
+        <v>491932</v>
       </c>
       <c r="R85" t="n">
-        <v>7024819</v>
+        <v>7024802</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10222,7 +10213,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135152803</v>
+        <v>135152802</v>
       </c>
       <c r="B86" t="n">
         <v>101403</v>
@@ -10265,10 +10256,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492030</v>
+        <v>491980</v>
       </c>
       <c r="R86" t="n">
-        <v>7024798</v>
+        <v>7024819</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10333,7 +10324,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135152804</v>
+        <v>135152803</v>
       </c>
       <c r="B87" t="n">
         <v>101403</v>
@@ -10376,10 +10367,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492027</v>
+        <v>492030</v>
       </c>
       <c r="R87" t="n">
-        <v>7024752</v>
+        <v>7024798</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10444,7 +10435,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>135152805</v>
+        <v>135152804</v>
       </c>
       <c r="B88" t="n">
         <v>101403</v>
@@ -10487,10 +10478,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>491959</v>
+        <v>492027</v>
       </c>
       <c r="R88" t="n">
-        <v>7024700</v>
+        <v>7024752</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10555,7 +10546,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>135152806</v>
+        <v>135152805</v>
       </c>
       <c r="B89" t="n">
         <v>101403</v>
@@ -10598,10 +10589,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492071</v>
+        <v>491959</v>
       </c>
       <c r="R89" t="n">
-        <v>7024723</v>
+        <v>7024700</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10666,7 +10657,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>135152807</v>
+        <v>135152806</v>
       </c>
       <c r="B90" t="n">
         <v>101403</v>
@@ -10709,10 +10700,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492009</v>
+        <v>492071</v>
       </c>
       <c r="R90" t="n">
-        <v>7024701</v>
+        <v>7024723</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10777,7 +10768,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>135152808</v>
+        <v>135152807</v>
       </c>
       <c r="B91" t="n">
         <v>101403</v>
@@ -10820,10 +10811,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>491915</v>
+        <v>492009</v>
       </c>
       <c r="R91" t="n">
-        <v>7024671</v>
+        <v>7024701</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10888,7 +10879,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>135152809</v>
+        <v>135152808</v>
       </c>
       <c r="B92" t="n">
         <v>101403</v>
@@ -10931,10 +10922,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>492020</v>
+        <v>491915</v>
       </c>
       <c r="R92" t="n">
-        <v>7024685</v>
+        <v>7024671</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10999,7 +10990,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>135152810</v>
+        <v>135152809</v>
       </c>
       <c r="B93" t="n">
         <v>101403</v>
@@ -11042,10 +11033,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>492028</v>
+        <v>492020</v>
       </c>
       <c r="R93" t="n">
-        <v>7024724</v>
+        <v>7024685</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -11110,7 +11101,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>135152811</v>
+        <v>135152810</v>
       </c>
       <c r="B94" t="n">
         <v>101403</v>
@@ -11153,10 +11144,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>492058</v>
+        <v>492028</v>
       </c>
       <c r="R94" t="n">
-        <v>7024705</v>
+        <v>7024724</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -11221,7 +11212,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>135152812</v>
+        <v>135152811</v>
       </c>
       <c r="B95" t="n">
         <v>101403</v>
@@ -11264,10 +11255,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492074</v>
+        <v>492058</v>
       </c>
       <c r="R95" t="n">
-        <v>7024686</v>
+        <v>7024705</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -11332,7 +11323,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>135152814</v>
+        <v>135152812</v>
       </c>
       <c r="B96" t="n">
         <v>101403</v>
@@ -11375,10 +11366,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492106</v>
+        <v>492074</v>
       </c>
       <c r="R96" t="n">
-        <v>7024668</v>
+        <v>7024686</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11443,10 +11434,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>135152780</v>
+        <v>135152814</v>
       </c>
       <c r="B97" t="n">
-        <v>98214</v>
+        <v>101403</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11454,21 +11445,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11486,10 +11477,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492108</v>
+        <v>492106</v>
       </c>
       <c r="R97" t="n">
-        <v>7024715</v>
+        <v>7024668</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11524,11 +11515,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD97" t="b">
         <v>0</v>
       </c>
@@ -11541,7 +11527,7 @@
       </c>
       <c r="AH97" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT97" t="inlineStr"/>
@@ -11559,7 +11545,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>135152781</v>
+        <v>135152780</v>
       </c>
       <c r="B98" t="n">
         <v>98214</v>
@@ -11602,10 +11588,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>491956</v>
+        <v>492108</v>
       </c>
       <c r="R98" t="n">
-        <v>7024753</v>
+        <v>7024715</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11640,6 +11626,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD98" t="b">
         <v>0</v>
       </c>
@@ -11652,12 +11643,7 @@
       </c>
       <c r="AH98" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT98" t="inlineStr"/>
@@ -11675,7 +11661,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>135152782</v>
+        <v>135152781</v>
       </c>
       <c r="B99" t="n">
         <v>98214</v>
@@ -11718,7 +11704,7 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492020</v>
+        <v>491956</v>
       </c>
       <c r="R99" t="n">
         <v>7024753</v>
@@ -11791,7 +11777,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>135152783</v>
+        <v>135152782</v>
       </c>
       <c r="B100" t="n">
         <v>98214</v>
@@ -11834,10 +11820,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492059</v>
+        <v>492020</v>
       </c>
       <c r="R100" t="n">
-        <v>7024724</v>
+        <v>7024753</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11907,7 +11893,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>135152784</v>
+        <v>135152783</v>
       </c>
       <c r="B101" t="n">
         <v>98214</v>
@@ -11950,10 +11936,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492019</v>
+        <v>492059</v>
       </c>
       <c r="R101" t="n">
-        <v>7024710</v>
+        <v>7024724</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11988,11 +11974,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Växer rikligt på fyndplatsen.</t>
-        </is>
-      </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
@@ -12010,7 +11991,7 @@
       </c>
       <c r="AI101" t="inlineStr">
         <is>
-          <t>Tydligt kalkpåverkad granskog.</t>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -12028,7 +12009,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>135152785</v>
+        <v>135152784</v>
       </c>
       <c r="B102" t="n">
         <v>98214</v>
@@ -12071,10 +12052,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>491995</v>
+        <v>492019</v>
       </c>
       <c r="R102" t="n">
-        <v>7024701</v>
+        <v>7024710</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -12111,7 +12092,7 @@
       </c>
       <c r="AC102" t="inlineStr">
         <is>
-          <t>Täcker ca 2 m2 yta i en sänka i kalkbarrskog.</t>
+          <t>Växer rikligt på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -12131,7 +12112,7 @@
       </c>
       <c r="AI102" t="inlineStr">
         <is>
-          <t>Med tydlig kalkpåverkan.</t>
+          <t>Tydligt kalkpåverkad granskog.</t>
         </is>
       </c>
       <c r="AT102" t="inlineStr"/>
@@ -12149,10 +12130,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>135152665</v>
+        <v>135152785</v>
       </c>
       <c r="B103" t="n">
-        <v>101305</v>
+        <v>98214</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12160,28 +12141,28 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L103" t="inlineStr"/>
@@ -12192,10 +12173,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492004</v>
+        <v>491995</v>
       </c>
       <c r="R103" t="n">
-        <v>7024816</v>
+        <v>7024701</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -12230,6 +12211,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Täcker ca 2 m2 yta i en sänka i kalkbarrskog.</t>
+        </is>
+      </c>
       <c r="AD103" t="b">
         <v>0</v>
       </c>
@@ -12242,12 +12228,12 @@
       </c>
       <c r="AH103" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI103" t="inlineStr">
         <is>
-          <t>Kalkgranskog.</t>
+          <t>Med tydlig kalkpåverkan.</t>
         </is>
       </c>
       <c r="AT103" t="inlineStr"/>
@@ -12265,10 +12251,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>135152666</v>
+        <v>135471205</v>
       </c>
       <c r="B104" t="n">
-        <v>101305</v>
+        <v>98214</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12276,42 +12262,50 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>491958</v>
+        <v>492009</v>
       </c>
       <c r="R104" t="n">
-        <v>7024801</v>
+        <v>7024701</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12338,12 +12332,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12356,27 +12350,22 @@
       <c r="AG104" t="b">
         <v>0</v>
       </c>
-      <c r="AH104" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>135152667</v>
+        <v>135152665</v>
       </c>
       <c r="B105" t="n">
         <v>101305</v>
@@ -12419,10 +12408,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>491931</v>
+        <v>492004</v>
       </c>
       <c r="R105" t="n">
-        <v>7024803</v>
+        <v>7024816</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12469,7 +12458,12 @@
       </c>
       <c r="AH105" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT105" t="inlineStr"/>
@@ -12487,7 +12481,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135152669</v>
+        <v>135152666</v>
       </c>
       <c r="B106" t="n">
         <v>101305</v>
@@ -12530,10 +12524,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>492033</v>
+        <v>491958</v>
       </c>
       <c r="R106" t="n">
-        <v>7024721</v>
+        <v>7024801</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12581,11 +12575,6 @@
       <c r="AH106" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI106" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT106" t="inlineStr"/>
@@ -12603,7 +12592,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>135152670</v>
+        <v>135152667</v>
       </c>
       <c r="B107" t="n">
         <v>101305</v>
@@ -12631,16 +12620,8 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J107" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
           <t>i frukt</t>
@@ -12654,10 +12635,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>491932</v>
+        <v>491931</v>
       </c>
       <c r="R107" t="n">
-        <v>7024733</v>
+        <v>7024803</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12692,11 +12673,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Bladen av svart trolldruva täcker här minst ca 4 m2 yta.</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -12710,11 +12686,6 @@
       <c r="AH107" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI107" t="inlineStr">
-        <is>
-          <t>Tydligt kalkpåverkad granskog.</t>
         </is>
       </c>
       <c r="AT107" t="inlineStr"/>
@@ -12732,10 +12703,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>135152729</v>
+        <v>135152669</v>
       </c>
       <c r="B108" t="n">
-        <v>99472</v>
+        <v>101305</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12743,16 +12714,16 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>222812</v>
+        <v>222771</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Liljekonvalj</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Convallaria majalis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -12764,7 +12735,7 @@
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L108" t="inlineStr"/>
@@ -12775,10 +12746,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>492067</v>
+        <v>492033</v>
       </c>
       <c r="R108" t="n">
-        <v>7024762</v>
+        <v>7024721</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12826,6 +12797,11 @@
       <c r="AH108" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI108" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT108" t="inlineStr"/>
@@ -12843,10 +12819,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>135152678</v>
+        <v>135152670</v>
       </c>
       <c r="B109" t="n">
-        <v>99001</v>
+        <v>101305</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12854,16 +12830,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>223049</v>
+        <v>222771</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -12871,8 +12847,16 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K109" t="inlineStr">
         <is>
           <t>i frukt</t>
@@ -12886,10 +12870,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>492100</v>
+        <v>491932</v>
       </c>
       <c r="R109" t="n">
-        <v>7024723</v>
+        <v>7024733</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12924,6 +12908,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Bladen av svart trolldruva täcker här minst ca 4 m2 yta.</t>
+        </is>
+      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
@@ -12937,6 +12926,11 @@
       <c r="AH109" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI109" t="inlineStr">
+        <is>
+          <t>Tydligt kalkpåverkad granskog.</t>
         </is>
       </c>
       <c r="AT109" t="inlineStr"/>
@@ -12954,10 +12948,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>135152679</v>
+        <v>135152729</v>
       </c>
       <c r="B110" t="n">
-        <v>99001</v>
+        <v>99472</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12965,16 +12959,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>223049</v>
+        <v>222812</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Liljekonvalj</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Convallaria majalis</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -12997,10 +12991,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>492072</v>
+        <v>492067</v>
       </c>
       <c r="R110" t="n">
-        <v>7024675</v>
+        <v>7024762</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -13065,7 +13059,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>135152680</v>
+        <v>135152678</v>
       </c>
       <c r="B111" t="n">
         <v>99001</v>
@@ -13097,7 +13091,7 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L111" t="inlineStr"/>
@@ -13108,10 +13102,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>492077</v>
+        <v>492100</v>
       </c>
       <c r="R111" t="n">
-        <v>7024765</v>
+        <v>7024723</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -13176,7 +13170,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>135152681</v>
+        <v>135152679</v>
       </c>
       <c r="B112" t="n">
         <v>99001</v>
@@ -13208,7 +13202,7 @@
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L112" t="inlineStr"/>
@@ -13219,10 +13213,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>491980</v>
+        <v>492072</v>
       </c>
       <c r="R112" t="n">
-        <v>7024784</v>
+        <v>7024675</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -13287,7 +13281,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>135152682</v>
+        <v>135152680</v>
       </c>
       <c r="B113" t="n">
         <v>99001</v>
@@ -13319,7 +13313,7 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
@@ -13330,10 +13324,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>492009</v>
+        <v>492077</v>
       </c>
       <c r="R113" t="n">
-        <v>7024787</v>
+        <v>7024765</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13398,7 +13392,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>135152683</v>
+        <v>135152681</v>
       </c>
       <c r="B114" t="n">
         <v>99001</v>
@@ -13441,10 +13435,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>491921</v>
+        <v>491980</v>
       </c>
       <c r="R114" t="n">
-        <v>7024666</v>
+        <v>7024784</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13509,7 +13503,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>135152684</v>
+        <v>135152682</v>
       </c>
       <c r="B115" t="n">
         <v>99001</v>
@@ -13552,10 +13546,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>492050</v>
+        <v>492009</v>
       </c>
       <c r="R115" t="n">
-        <v>7024700</v>
+        <v>7024787</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13620,10 +13614,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>135152685</v>
+        <v>135152683</v>
       </c>
       <c r="B116" t="n">
-        <v>101293</v>
+        <v>99001</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13631,28 +13625,28 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>224885</v>
+        <v>223049</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
@@ -13663,10 +13657,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>492048</v>
+        <v>491921</v>
       </c>
       <c r="R116" t="n">
-        <v>7024654</v>
+        <v>7024666</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13731,10 +13725,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>135152686</v>
+        <v>135152684</v>
       </c>
       <c r="B117" t="n">
-        <v>101293</v>
+        <v>99001</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13742,28 +13736,28 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>224885</v>
+        <v>223049</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L117" t="inlineStr"/>
@@ -13774,10 +13768,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>492053</v>
+        <v>492050</v>
       </c>
       <c r="R117" t="n">
-        <v>7024691</v>
+        <v>7024700</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13842,7 +13836,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>135152687</v>
+        <v>135152685</v>
       </c>
       <c r="B118" t="n">
         <v>101293</v>
@@ -13874,7 +13868,7 @@
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
@@ -13885,10 +13879,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>492083</v>
+        <v>492048</v>
       </c>
       <c r="R118" t="n">
-        <v>7024682</v>
+        <v>7024654</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13953,7 +13947,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>135152688</v>
+        <v>135152686</v>
       </c>
       <c r="B119" t="n">
         <v>101293</v>
@@ -13985,7 +13979,7 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
@@ -13996,10 +13990,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>492067</v>
+        <v>492053</v>
       </c>
       <c r="R119" t="n">
-        <v>7024728</v>
+        <v>7024691</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -14064,7 +14058,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>135152689</v>
+        <v>135152687</v>
       </c>
       <c r="B120" t="n">
         <v>101293</v>
@@ -14096,7 +14090,7 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L120" t="inlineStr"/>
@@ -14107,10 +14101,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>492080</v>
+        <v>492083</v>
       </c>
       <c r="R120" t="n">
-        <v>7024749</v>
+        <v>7024682</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -14175,7 +14169,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>135152690</v>
+        <v>135152688</v>
       </c>
       <c r="B121" t="n">
         <v>101293</v>
@@ -14207,7 +14201,7 @@
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L121" t="inlineStr"/>
@@ -14218,10 +14212,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>492038</v>
+        <v>492067</v>
       </c>
       <c r="R121" t="n">
-        <v>7024754</v>
+        <v>7024728</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -14286,7 +14280,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>135152691</v>
+        <v>135152689</v>
       </c>
       <c r="B122" t="n">
         <v>101293</v>
@@ -14318,7 +14312,7 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L122" t="inlineStr"/>
@@ -14329,10 +14323,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>492066</v>
+        <v>492080</v>
       </c>
       <c r="R122" t="n">
-        <v>7024765</v>
+        <v>7024749</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14397,7 +14391,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>135152693</v>
+        <v>135152690</v>
       </c>
       <c r="B123" t="n">
         <v>101293</v>
@@ -14440,10 +14434,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>492089</v>
+        <v>492038</v>
       </c>
       <c r="R123" t="n">
-        <v>7024769</v>
+        <v>7024754</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14490,7 +14484,7 @@
       </c>
       <c r="AH123" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT123" t="inlineStr"/>
@@ -14508,7 +14502,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>135152694</v>
+        <v>135152691</v>
       </c>
       <c r="B124" t="n">
         <v>101293</v>
@@ -14551,10 +14545,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>492064</v>
+        <v>492066</v>
       </c>
       <c r="R124" t="n">
-        <v>7024777</v>
+        <v>7024765</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14619,7 +14613,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>135152695</v>
+        <v>135152693</v>
       </c>
       <c r="B125" t="n">
         <v>101293</v>
@@ -14651,7 +14645,7 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
@@ -14662,10 +14656,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>491980</v>
+        <v>492089</v>
       </c>
       <c r="R125" t="n">
-        <v>7024778</v>
+        <v>7024769</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14712,7 +14706,7 @@
       </c>
       <c r="AH125" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AT125" t="inlineStr"/>
@@ -14730,7 +14724,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>135152696</v>
+        <v>135152694</v>
       </c>
       <c r="B126" t="n">
         <v>101293</v>
@@ -14773,10 +14767,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>492025</v>
+        <v>492064</v>
       </c>
       <c r="R126" t="n">
-        <v>7024786</v>
+        <v>7024777</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14841,7 +14835,7 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>135152697</v>
+        <v>135152695</v>
       </c>
       <c r="B127" t="n">
         <v>101293</v>
@@ -14873,7 +14867,7 @@
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
@@ -14884,10 +14878,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>492005</v>
+        <v>491980</v>
       </c>
       <c r="R127" t="n">
-        <v>7024801</v>
+        <v>7024778</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14952,7 +14946,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>135152698</v>
+        <v>135152696</v>
       </c>
       <c r="B128" t="n">
         <v>101293</v>
@@ -14984,7 +14978,7 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
@@ -14995,10 +14989,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>491947</v>
+        <v>492025</v>
       </c>
       <c r="R128" t="n">
-        <v>7024802</v>
+        <v>7024786</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -15063,7 +15057,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>135152700</v>
+        <v>135152697</v>
       </c>
       <c r="B129" t="n">
         <v>101293</v>
@@ -15106,10 +15100,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>492010</v>
+        <v>492005</v>
       </c>
       <c r="R129" t="n">
-        <v>7024787</v>
+        <v>7024801</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -15174,7 +15168,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>135152701</v>
+        <v>135152698</v>
       </c>
       <c r="B130" t="n">
         <v>101293</v>
@@ -15217,10 +15211,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>492020</v>
+        <v>491947</v>
       </c>
       <c r="R130" t="n">
-        <v>7024800</v>
+        <v>7024802</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -15285,7 +15279,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>135152702</v>
+        <v>135152700</v>
       </c>
       <c r="B131" t="n">
         <v>101293</v>
@@ -15328,10 +15322,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>491991</v>
+        <v>492010</v>
       </c>
       <c r="R131" t="n">
-        <v>7024745</v>
+        <v>7024787</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15396,7 +15390,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>135152703</v>
+        <v>135152701</v>
       </c>
       <c r="B132" t="n">
         <v>101293</v>
@@ -15428,7 +15422,7 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
@@ -15439,10 +15433,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>492022</v>
+        <v>492020</v>
       </c>
       <c r="R132" t="n">
-        <v>7024756</v>
+        <v>7024800</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15507,7 +15501,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>135152704</v>
+        <v>135152702</v>
       </c>
       <c r="B133" t="n">
         <v>101293</v>
@@ -15539,7 +15533,7 @@
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
@@ -15550,10 +15544,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>491964</v>
+        <v>491991</v>
       </c>
       <c r="R133" t="n">
-        <v>7024702</v>
+        <v>7024745</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15618,7 +15612,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>135152705</v>
+        <v>135152703</v>
       </c>
       <c r="B134" t="n">
         <v>101293</v>
@@ -15661,10 +15655,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>492081</v>
+        <v>492022</v>
       </c>
       <c r="R134" t="n">
-        <v>7024728</v>
+        <v>7024756</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15729,7 +15723,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135152706</v>
+        <v>135152704</v>
       </c>
       <c r="B135" t="n">
         <v>101293</v>
@@ -15761,7 +15755,7 @@
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
@@ -15772,10 +15766,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>491979</v>
+        <v>491964</v>
       </c>
       <c r="R135" t="n">
-        <v>7024678</v>
+        <v>7024702</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15840,7 +15834,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135152707</v>
+        <v>135152705</v>
       </c>
       <c r="B136" t="n">
         <v>101293</v>
@@ -15883,10 +15877,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>491913</v>
+        <v>492081</v>
       </c>
       <c r="R136" t="n">
-        <v>7024670</v>
+        <v>7024728</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15951,7 +15945,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>135152708</v>
+        <v>135152706</v>
       </c>
       <c r="B137" t="n">
         <v>101293</v>
@@ -15983,7 +15977,7 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
@@ -15994,10 +15988,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>491922</v>
+        <v>491979</v>
       </c>
       <c r="R137" t="n">
-        <v>7024707</v>
+        <v>7024678</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -16030,11 +16024,6 @@
       <c r="AA137" t="inlineStr">
         <is>
           <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC137" t="inlineStr">
-        <is>
-          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -16067,7 +16056,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>135152709</v>
+        <v>135152707</v>
       </c>
       <c r="B138" t="n">
         <v>101293</v>
@@ -16099,7 +16088,7 @@
       <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
@@ -16110,10 +16099,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>491938</v>
+        <v>491913</v>
       </c>
       <c r="R138" t="n">
-        <v>7024737</v>
+        <v>7024670</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -16178,7 +16167,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>135152710</v>
+        <v>135152708</v>
       </c>
       <c r="B139" t="n">
         <v>101293</v>
@@ -16210,7 +16199,7 @@
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
@@ -16221,10 +16210,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>492009</v>
+        <v>491922</v>
       </c>
       <c r="R139" t="n">
-        <v>7024659</v>
+        <v>7024707</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -16257,6 +16246,11 @@
       <c r="AA139" t="inlineStr">
         <is>
           <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Rikligt!</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16289,7 +16283,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>135152711</v>
+        <v>135152709</v>
       </c>
       <c r="B140" t="n">
         <v>101293</v>
@@ -16321,7 +16315,7 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
@@ -16332,10 +16326,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>492017</v>
+        <v>491938</v>
       </c>
       <c r="R140" t="n">
-        <v>7024711</v>
+        <v>7024737</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16400,7 +16394,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135152712</v>
+        <v>135152710</v>
       </c>
       <c r="B141" t="n">
         <v>101293</v>
@@ -16432,7 +16426,7 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
@@ -16443,10 +16437,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>492059</v>
+        <v>492009</v>
       </c>
       <c r="R141" t="n">
-        <v>7024704</v>
+        <v>7024659</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16511,7 +16505,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>135152713</v>
+        <v>135152711</v>
       </c>
       <c r="B142" t="n">
         <v>101293</v>
@@ -16554,10 +16548,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>492108</v>
+        <v>492017</v>
       </c>
       <c r="R142" t="n">
-        <v>7024672</v>
+        <v>7024711</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16619,6 +16613,228 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>135152712</v>
+      </c>
+      <c r="B143" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>492059</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7024704</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH143" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>135152713</v>
+      </c>
+      <c r="B144" t="n">
+        <v>101293</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>492108</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7024672</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH144" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY144"/>
+  <dimension ref="A1:AZ144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152737</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152738</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152739</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152740</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152741</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152742</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152743</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152744</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152745</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152746</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152747</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152748</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152749</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152751</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152752</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152753</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2496,6 +2581,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152754</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2608,6 +2698,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152755</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2715,6 +2810,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152756</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2822,6 +2922,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152757</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2929,6 +3034,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152758</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3036,6 +3146,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152759</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3143,6 +3258,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152761</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3250,6 +3370,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152762</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3357,6 +3482,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152763</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3464,6 +3594,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152764</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3571,6 +3706,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152765</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3678,6 +3818,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152766</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3785,6 +3930,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152767</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3892,6 +4042,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152768</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4023,6 +4178,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152773</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4149,6 +4309,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152774</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4275,6 +4440,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152775</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4405,6 +4575,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152714</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4536,6 +4711,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152715</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4667,6 +4847,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152716</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4798,6 +4983,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152717</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4933,6 +5123,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152671</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5068,6 +5263,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152672</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5198,6 +5398,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152673</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5328,6 +5533,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152718</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5458,6 +5668,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152721</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5588,6 +5803,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152722</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5720,6 +5940,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152661</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5848,6 +6073,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152663</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5970,6 +6200,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152676</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6086,6 +6321,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152777</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6202,6 +6442,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152778</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6318,6 +6563,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152779</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6420,6 +6670,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471439</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6531,6 +6786,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152655</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6647,6 +6907,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152656</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6758,6 +7023,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152657</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6874,6 +7144,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152658</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6990,6 +7265,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152659</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7101,6 +7381,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152736</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7212,6 +7497,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152786</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7323,6 +7613,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152787</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7434,6 +7729,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152788</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7545,6 +7845,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152789</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7656,6 +7961,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152730</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7767,6 +8077,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152731</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7878,6 +8193,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152732</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7985,6 +8305,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152733</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8096,6 +8421,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152734</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8207,6 +8537,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152735</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8318,6 +8653,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152723</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8429,6 +8769,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152724</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8540,6 +8885,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152726</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8651,6 +9001,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152727</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8762,6 +9117,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152728</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8878,6 +9238,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152646</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8989,6 +9354,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152674</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9100,6 +9470,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152791</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9211,6 +9586,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152792</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9322,6 +9702,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152793</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9433,6 +9818,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152794</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9544,6 +9934,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152795</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9655,6 +10050,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152796</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9766,6 +10166,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152797</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9877,6 +10282,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152798</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9988,6 +10398,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152799</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -10099,6 +10514,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152800</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10210,6 +10630,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152801</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10321,6 +10746,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152802</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10432,6 +10862,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152803</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10543,6 +10978,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152804</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10654,6 +11094,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152805</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10765,6 +11210,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152806</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10876,6 +11326,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152807</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10987,6 +11442,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152808</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -11098,6 +11558,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152809</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -11209,6 +11674,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152810</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -11320,6 +11790,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152811</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -11431,6 +11906,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152812</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11542,6 +12022,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152814</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11658,6 +12143,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152780</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11774,6 +12264,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152781</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11890,6 +12385,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152782</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -12006,6 +12506,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152783</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -12127,6 +12632,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152784</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -12248,6 +12758,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152785</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -12362,6 +12877,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135471205</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -12478,6 +12998,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152665</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12589,6 +13114,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152666</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12700,6 +13230,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152667</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12816,6 +13351,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152669</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12945,6 +13485,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152670</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -13056,6 +13601,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152729</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -13167,6 +13717,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152678</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -13278,6 +13833,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152679</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -13389,6 +13949,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152680</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -13500,6 +14065,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152681</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13611,6 +14181,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152682</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13722,6 +14297,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152683</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13833,6 +14413,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152684</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13944,6 +14529,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -14055,6 +14645,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152686</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -14166,6 +14761,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152687</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -14277,6 +14877,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152688</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -14388,6 +14993,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152689</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -14499,6 +15109,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152690</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14610,6 +15225,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152691</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14721,6 +15341,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14832,6 +15457,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152694</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14943,6 +15573,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152695</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -15054,6 +15689,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152696</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -15165,6 +15805,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152697</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -15276,6 +15921,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152698</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -15387,6 +16037,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152700</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -15498,6 +16153,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152701</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15609,6 +16269,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152702</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15720,6 +16385,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152703</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15831,6 +16501,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152704</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15942,6 +16617,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152705</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -16053,6 +16733,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152706</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -16164,6 +16849,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152707</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -16280,6 +16970,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152708</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -16391,6 +17086,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152709</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -16502,6 +17202,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152710</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16613,6 +17318,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152711</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16724,6 +17434,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152712</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16835,8 +17550,158 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152713</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135152737</v>
       </c>
       <c r="B2" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135152738</v>
       </c>
       <c r="B3" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135152739</v>
       </c>
       <c r="B4" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135152740</v>
       </c>
       <c r="B5" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135152741</v>
       </c>
       <c r="B6" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135152742</v>
       </c>
       <c r="B7" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135152743</v>
       </c>
       <c r="B8" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135152744</v>
       </c>
       <c r="B9" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135152745</v>
       </c>
       <c r="B10" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135152746</v>
       </c>
       <c r="B11" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135152747</v>
       </c>
       <c r="B12" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135152748</v>
       </c>
       <c r="B13" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>135152749</v>
       </c>
       <c r="B14" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135152751</v>
       </c>
       <c r="B15" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135152752</v>
       </c>
       <c r="B16" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135152753</v>
       </c>
       <c r="B17" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>135152754</v>
       </c>
       <c r="B18" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135152755</v>
       </c>
       <c r="B19" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135152756</v>
       </c>
       <c r="B20" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135152757</v>
       </c>
       <c r="B21" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135152758</v>
       </c>
       <c r="B22" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>135152759</v>
       </c>
       <c r="B23" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>135152761</v>
       </c>
       <c r="B24" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>135152762</v>
       </c>
       <c r="B25" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>135152763</v>
       </c>
       <c r="B26" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>135152764</v>
       </c>
       <c r="B27" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>135152765</v>
       </c>
       <c r="B28" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>135152766</v>
       </c>
       <c r="B29" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>135152767</v>
       </c>
       <c r="B30" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>135152768</v>
       </c>
       <c r="B31" t="n">
-        <v>96410</v>
+        <v>96454</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135152773</v>
       </c>
       <c r="B32" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>135152774</v>
       </c>
       <c r="B33" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>135152775</v>
       </c>
       <c r="B34" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>135152714</v>
       </c>
       <c r="B35" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>135152715</v>
       </c>
       <c r="B36" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>135152716</v>
       </c>
       <c r="B37" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>135152717</v>
       </c>
       <c r="B38" t="n">
-        <v>80488</v>
+        <v>80526</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>135152671</v>
       </c>
       <c r="B39" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>135152672</v>
       </c>
       <c r="B40" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>135152673</v>
       </c>
       <c r="B41" t="n">
-        <v>80493</v>
+        <v>80531</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>135152718</v>
       </c>
       <c r="B42" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135152721</v>
       </c>
       <c r="B43" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>135152722</v>
       </c>
       <c r="B44" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>135152661</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>135152663</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>135152676</v>
       </c>
       <c r="B47" t="n">
-        <v>58410</v>
+        <v>58415</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>135152777</v>
       </c>
       <c r="B48" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>135152778</v>
       </c>
       <c r="B49" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>135152779</v>
       </c>
       <c r="B50" t="n">
-        <v>99112</v>
+        <v>99159</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>135471439</v>
       </c>
       <c r="B51" t="n">
-        <v>98219</v>
+        <v>98263</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>135152655</v>
       </c>
       <c r="B52" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>135152656</v>
       </c>
       <c r="B53" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>135152657</v>
       </c>
       <c r="B54" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>135152658</v>
       </c>
       <c r="B55" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>135152659</v>
       </c>
       <c r="B56" t="n">
-        <v>99219</v>
+        <v>99266</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>135152736</v>
       </c>
       <c r="B57" t="n">
-        <v>99533</v>
+        <v>99580</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>135152786</v>
       </c>
       <c r="B58" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>135152787</v>
       </c>
       <c r="B59" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>135152788</v>
       </c>
       <c r="B60" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>135152789</v>
       </c>
       <c r="B61" t="n">
-        <v>108205</v>
+        <v>108260</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>135152730</v>
       </c>
       <c r="B62" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>135152731</v>
       </c>
       <c r="B63" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>135152732</v>
       </c>
       <c r="B64" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>135152733</v>
       </c>
       <c r="B65" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>135152734</v>
       </c>
       <c r="B66" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>135152735</v>
       </c>
       <c r="B67" t="n">
-        <v>108274</v>
+        <v>108330</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>135152723</v>
       </c>
       <c r="B68" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>135152724</v>
       </c>
       <c r="B69" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>135152726</v>
       </c>
       <c r="B70" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>135152727</v>
       </c>
       <c r="B71" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>135152728</v>
       </c>
       <c r="B72" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>135152646</v>
       </c>
       <c r="B73" t="n">
-        <v>106309</v>
+        <v>106364</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>135152674</v>
       </c>
       <c r="B74" t="n">
-        <v>99217</v>
+        <v>99264</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135152791</v>
       </c>
       <c r="B75" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>135152792</v>
       </c>
       <c r="B76" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>135152793</v>
       </c>
       <c r="B77" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>135152794</v>
       </c>
       <c r="B78" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>135152795</v>
       </c>
       <c r="B79" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>135152796</v>
       </c>
       <c r="B80" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>135152797</v>
       </c>
       <c r="B81" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>135152798</v>
       </c>
       <c r="B82" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>135152799</v>
       </c>
       <c r="B83" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>135152800</v>
       </c>
       <c r="B84" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>135152801</v>
       </c>
       <c r="B85" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>135152802</v>
       </c>
       <c r="B86" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>135152803</v>
       </c>
       <c r="B87" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>135152804</v>
       </c>
       <c r="B88" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>135152805</v>
       </c>
       <c r="B89" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>135152806</v>
       </c>
       <c r="B90" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>135152807</v>
       </c>
       <c r="B91" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>135152808</v>
       </c>
       <c r="B92" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>135152809</v>
       </c>
       <c r="B93" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>135152810</v>
       </c>
       <c r="B94" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>135152811</v>
       </c>
       <c r="B95" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>135152812</v>
       </c>
       <c r="B96" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>135152814</v>
       </c>
       <c r="B97" t="n">
-        <v>101403</v>
+        <v>101451</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>135152780</v>
       </c>
       <c r="B98" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>135152781</v>
       </c>
       <c r="B99" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>135152782</v>
       </c>
       <c r="B100" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>135152783</v>
       </c>
       <c r="B101" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>135152784</v>
       </c>
       <c r="B102" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>135152785</v>
       </c>
       <c r="B103" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>135471205</v>
       </c>
       <c r="B104" t="n">
-        <v>98214</v>
+        <v>98258</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>135152665</v>
       </c>
       <c r="B105" t="n">
-        <v>101305</v>
+        <v>101353</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>135152666</v>
       </c>
       <c r="B106" t="n">
-        <v>101305</v>
+        <v>101353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>135152667</v>
       </c>
       <c r="B107" t="n">
-        <v>101305</v>
+        <v>101353</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>135152669</v>
       </c>
       <c r="B108" t="n">
-        <v>101305</v>
+        <v>101353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>135152670</v>
       </c>
       <c r="B109" t="n">
-        <v>101305</v>
+        <v>101353</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>135152729</v>
       </c>
       <c r="B110" t="n">
-        <v>99472</v>
+        <v>99519</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>135152678</v>
       </c>
       <c r="B111" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>135152679</v>
       </c>
       <c r="B112" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>135152680</v>
       </c>
       <c r="B113" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>135152681</v>
       </c>
       <c r="B114" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>135152682</v>
       </c>
       <c r="B115" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>135152683</v>
       </c>
       <c r="B116" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>135152684</v>
       </c>
       <c r="B117" t="n">
-        <v>99001</v>
+        <v>99048</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>135152685</v>
       </c>
       <c r="B118" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>135152686</v>
       </c>
       <c r="B119" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>135152687</v>
       </c>
       <c r="B120" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>135152688</v>
       </c>
       <c r="B121" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>135152689</v>
       </c>
       <c r="B122" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>135152690</v>
       </c>
       <c r="B123" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>135152691</v>
       </c>
       <c r="B124" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>135152693</v>
       </c>
       <c r="B125" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>135152694</v>
       </c>
       <c r="B126" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>135152695</v>
       </c>
       <c r="B127" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>135152696</v>
       </c>
       <c r="B128" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>135152697</v>
       </c>
       <c r="B129" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>135152698</v>
       </c>
       <c r="B130" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>135152700</v>
       </c>
       <c r="B131" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>135152701</v>
       </c>
       <c r="B132" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>135152702</v>
       </c>
       <c r="B133" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>135152703</v>
       </c>
       <c r="B134" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>135152704</v>
       </c>
       <c r="B135" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>135152705</v>
       </c>
       <c r="B136" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>135152706</v>
       </c>
       <c r="B137" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>135152707</v>
       </c>
       <c r="B138" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>135152708</v>
       </c>
       <c r="B139" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>135152709</v>
       </c>
       <c r="B140" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>135152710</v>
       </c>
       <c r="B141" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>135152711</v>
       </c>
       <c r="B142" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>135152712</v>
       </c>
       <c r="B143" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>135152713</v>
       </c>
       <c r="B144" t="n">
-        <v>101293</v>
+        <v>101341</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135152737</v>
       </c>
       <c r="B2" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135152738</v>
       </c>
       <c r="B3" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135152739</v>
       </c>
       <c r="B4" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135152740</v>
       </c>
       <c r="B5" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>135152741</v>
       </c>
       <c r="B6" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>135152742</v>
       </c>
       <c r="B7" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>135152743</v>
       </c>
       <c r="B8" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         <v>135152744</v>
       </c>
       <c r="B9" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1584,7 +1584,7 @@
         <v>135152745</v>
       </c>
       <c r="B10" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1696,7 +1696,7 @@
         <v>135152746</v>
       </c>
       <c r="B11" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>135152747</v>
       </c>
       <c r="B12" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>135152748</v>
       </c>
       <c r="B13" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>135152749</v>
       </c>
       <c r="B14" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>135152751</v>
       </c>
       <c r="B15" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>135152752</v>
       </c>
       <c r="B16" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>135152753</v>
       </c>
       <c r="B17" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>135152754</v>
       </c>
       <c r="B18" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>135152755</v>
       </c>
       <c r="B19" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>135152756</v>
       </c>
       <c r="B20" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>135152757</v>
       </c>
       <c r="B21" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>135152758</v>
       </c>
       <c r="B22" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
         <v>135152759</v>
       </c>
       <c r="B23" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>135152761</v>
       </c>
       <c r="B24" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>135152762</v>
       </c>
       <c r="B25" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>135152763</v>
       </c>
       <c r="B26" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3493,7 +3493,7 @@
         <v>135152764</v>
       </c>
       <c r="B27" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>135152765</v>
       </c>
       <c r="B28" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3717,7 +3717,7 @@
         <v>135152766</v>
       </c>
       <c r="B29" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
         <v>135152767</v>
       </c>
       <c r="B30" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>135152768</v>
       </c>
       <c r="B31" t="n">
-        <v>96454</v>
+        <v>96481</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4053,7 +4053,7 @@
         <v>135152773</v>
       </c>
       <c r="B32" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>135152774</v>
       </c>
       <c r="B33" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>135152775</v>
       </c>
       <c r="B34" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4451,7 +4451,7 @@
         <v>135152714</v>
       </c>
       <c r="B35" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>135152715</v>
       </c>
       <c r="B36" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>135152716</v>
       </c>
       <c r="B37" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
         <v>135152717</v>
       </c>
       <c r="B38" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4994,7 +4994,7 @@
         <v>135152671</v>
       </c>
       <c r="B39" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>135152672</v>
       </c>
       <c r="B40" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
         <v>135152673</v>
       </c>
       <c r="B41" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>135152718</v>
       </c>
       <c r="B42" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>135152721</v>
       </c>
       <c r="B43" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5679,7 +5679,7 @@
         <v>135152722</v>
       </c>
       <c r="B44" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
         <v>135152777</v>
       </c>
       <c r="B48" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>135152778</v>
       </c>
       <c r="B49" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6453,7 +6453,7 @@
         <v>135152779</v>
       </c>
       <c r="B50" t="n">
-        <v>99159</v>
+        <v>99186</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>135471439</v>
       </c>
       <c r="B51" t="n">
-        <v>98263</v>
+        <v>98290</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6681,7 +6681,7 @@
         <v>135152655</v>
       </c>
       <c r="B52" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>135152656</v>
       </c>
       <c r="B53" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>135152657</v>
       </c>
       <c r="B54" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         <v>135152658</v>
       </c>
       <c r="B55" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>135152659</v>
       </c>
       <c r="B56" t="n">
-        <v>99266</v>
+        <v>99293</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7276,7 +7276,7 @@
         <v>135152736</v>
       </c>
       <c r="B57" t="n">
-        <v>99580</v>
+        <v>99607</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7392,7 +7392,7 @@
         <v>135152786</v>
       </c>
       <c r="B58" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>135152787</v>
       </c>
       <c r="B59" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>135152788</v>
       </c>
       <c r="B60" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7740,7 +7740,7 @@
         <v>135152789</v>
       </c>
       <c r="B61" t="n">
-        <v>108260</v>
+        <v>108287</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>135152730</v>
       </c>
       <c r="B62" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7972,7 +7972,7 @@
         <v>135152731</v>
       </c>
       <c r="B63" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>135152732</v>
       </c>
       <c r="B64" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>135152733</v>
       </c>
       <c r="B65" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>135152734</v>
       </c>
       <c r="B66" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>135152735</v>
       </c>
       <c r="B67" t="n">
-        <v>108330</v>
+        <v>108357</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8548,7 +8548,7 @@
         <v>135152723</v>
       </c>
       <c r="B68" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>135152724</v>
       </c>
       <c r="B69" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8780,7 +8780,7 @@
         <v>135152726</v>
       </c>
       <c r="B70" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>135152727</v>
       </c>
       <c r="B71" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>135152728</v>
       </c>
       <c r="B72" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9128,7 +9128,7 @@
         <v>135152646</v>
       </c>
       <c r="B73" t="n">
-        <v>106364</v>
+        <v>106391</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -9249,7 +9249,7 @@
         <v>135152674</v>
       </c>
       <c r="B74" t="n">
-        <v>99264</v>
+        <v>99291</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9365,7 +9365,7 @@
         <v>135152791</v>
       </c>
       <c r="B75" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>135152792</v>
       </c>
       <c r="B76" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>135152793</v>
       </c>
       <c r="B77" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>135152794</v>
       </c>
       <c r="B78" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9829,7 +9829,7 @@
         <v>135152795</v>
       </c>
       <c r="B79" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>135152796</v>
       </c>
       <c r="B80" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10061,7 +10061,7 @@
         <v>135152797</v>
       </c>
       <c r="B81" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>135152798</v>
       </c>
       <c r="B82" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>135152799</v>
       </c>
       <c r="B83" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>135152800</v>
       </c>
       <c r="B84" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>135152801</v>
       </c>
       <c r="B85" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10641,7 +10641,7 @@
         <v>135152802</v>
       </c>
       <c r="B86" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>135152803</v>
       </c>
       <c r="B87" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>135152804</v>
       </c>
       <c r="B88" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10989,7 +10989,7 @@
         <v>135152805</v>
       </c>
       <c r="B89" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11105,7 +11105,7 @@
         <v>135152806</v>
       </c>
       <c r="B90" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>135152807</v>
       </c>
       <c r="B91" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -11337,7 +11337,7 @@
         <v>135152808</v>
       </c>
       <c r="B92" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>135152809</v>
       </c>
       <c r="B93" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11569,7 +11569,7 @@
         <v>135152810</v>
       </c>
       <c r="B94" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11685,7 +11685,7 @@
         <v>135152811</v>
       </c>
       <c r="B95" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11801,7 +11801,7 @@
         <v>135152812</v>
       </c>
       <c r="B96" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11917,7 +11917,7 @@
         <v>135152814</v>
       </c>
       <c r="B97" t="n">
-        <v>101451</v>
+        <v>101478</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12033,7 +12033,7 @@
         <v>135152780</v>
       </c>
       <c r="B98" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12154,7 +12154,7 @@
         <v>135152781</v>
       </c>
       <c r="B99" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12275,7 +12275,7 @@
         <v>135152782</v>
       </c>
       <c r="B100" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -12396,7 +12396,7 @@
         <v>135152783</v>
       </c>
       <c r="B101" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>135152784</v>
       </c>
       <c r="B102" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12643,7 +12643,7 @@
         <v>135152785</v>
       </c>
       <c r="B103" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12769,7 +12769,7 @@
         <v>135471205</v>
       </c>
       <c r="B104" t="n">
-        <v>98258</v>
+        <v>98285</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12888,7 +12888,7 @@
         <v>135152665</v>
       </c>
       <c r="B105" t="n">
-        <v>101353</v>
+        <v>101380</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13009,7 +13009,7 @@
         <v>135152666</v>
       </c>
       <c r="B106" t="n">
-        <v>101353</v>
+        <v>101380</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13125,7 +13125,7 @@
         <v>135152667</v>
       </c>
       <c r="B107" t="n">
-        <v>101353</v>
+        <v>101380</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>135152669</v>
       </c>
       <c r="B108" t="n">
-        <v>101353</v>
+        <v>101380</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13362,7 +13362,7 @@
         <v>135152670</v>
       </c>
       <c r="B109" t="n">
-        <v>101353</v>
+        <v>101380</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>135152729</v>
       </c>
       <c r="B110" t="n">
-        <v>99519</v>
+        <v>99546</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13612,7 +13612,7 @@
         <v>135152678</v>
       </c>
       <c r="B111" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13728,7 +13728,7 @@
         <v>135152679</v>
       </c>
       <c r="B112" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13844,7 +13844,7 @@
         <v>135152680</v>
       </c>
       <c r="B113" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13960,7 +13960,7 @@
         <v>135152681</v>
       </c>
       <c r="B114" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>135152682</v>
       </c>
       <c r="B115" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14192,7 +14192,7 @@
         <v>135152683</v>
       </c>
       <c r="B116" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>135152684</v>
       </c>
       <c r="B117" t="n">
-        <v>99048</v>
+        <v>99075</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>135152685</v>
       </c>
       <c r="B118" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14540,7 +14540,7 @@
         <v>135152686</v>
       </c>
       <c r="B119" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>135152687</v>
       </c>
       <c r="B120" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>135152688</v>
       </c>
       <c r="B121" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>135152689</v>
       </c>
       <c r="B122" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>135152690</v>
       </c>
       <c r="B123" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -15120,7 +15120,7 @@
         <v>135152691</v>
       </c>
       <c r="B124" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>135152693</v>
       </c>
       <c r="B125" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>135152694</v>
       </c>
       <c r="B126" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>135152695</v>
       </c>
       <c r="B127" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>135152696</v>
       </c>
       <c r="B128" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15700,7 +15700,7 @@
         <v>135152697</v>
       </c>
       <c r="B129" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>135152698</v>
       </c>
       <c r="B130" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15932,7 +15932,7 @@
         <v>135152700</v>
       </c>
       <c r="B131" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -16048,7 +16048,7 @@
         <v>135152701</v>
       </c>
       <c r="B132" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>135152702</v>
       </c>
       <c r="B133" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16280,7 +16280,7 @@
         <v>135152703</v>
       </c>
       <c r="B134" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16396,7 +16396,7 @@
         <v>135152704</v>
       </c>
       <c r="B135" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>135152705</v>
       </c>
       <c r="B136" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16628,7 +16628,7 @@
         <v>135152706</v>
       </c>
       <c r="B137" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>135152707</v>
       </c>
       <c r="B138" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16860,7 +16860,7 @@
         <v>135152708</v>
       </c>
       <c r="B139" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>135152709</v>
       </c>
       <c r="B140" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -17097,7 +17097,7 @@
         <v>135152710</v>
       </c>
       <c r="B141" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17213,7 +17213,7 @@
         <v>135152711</v>
       </c>
       <c r="B142" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17329,7 +17329,7 @@
         <v>135152712</v>
       </c>
       <c r="B143" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>135152713</v>
       </c>
       <c r="B144" t="n">
-        <v>101341</v>
+        <v>101368</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2390,10 +2390,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135152656</v>
+        <v>135471439</v>
       </c>
       <c r="B15" t="n">
-        <v>99293</v>
+        <v>98295</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2401,45 +2401,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219847</v>
+        <v>219815</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492109</v>
+        <v>491957</v>
       </c>
       <c r="R15" t="n">
-        <v>7024713</v>
+        <v>7024690</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2463,17 +2459,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2486,35 +2477,30 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Rikkärr med barrträd</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152736</v>
+        <v>135152656</v>
       </c>
       <c r="B16" t="n">
-        <v>99607</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2522,28 +2508,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219880</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2554,10 +2540,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492090</v>
+        <v>492109</v>
       </c>
       <c r="R16" t="n">
-        <v>7024764</v>
+        <v>7024713</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2592,6 +2578,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2604,7 +2595,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2621,16 +2612,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135152787</v>
+        <v>135152736</v>
       </c>
       <c r="B17" t="n">
-        <v>108287</v>
+        <v>99607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2638,21 +2629,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220083</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2670,10 +2661,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492029</v>
+        <v>492090</v>
       </c>
       <c r="R17" t="n">
-        <v>7024730</v>
+        <v>7024764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2737,16 +2728,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152735</v>
+        <v>135152787</v>
       </c>
       <c r="B18" t="n">
-        <v>108357</v>
+        <v>108287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2754,28 +2745,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220102</v>
+        <v>220083</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2786,10 +2777,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491933</v>
+        <v>492029</v>
       </c>
       <c r="R18" t="n">
-        <v>7024735</v>
+        <v>7024730</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2853,16 +2844,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152646</v>
+        <v>135152735</v>
       </c>
       <c r="B19" t="n">
-        <v>106391</v>
+        <v>108357</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2870,28 +2861,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221725</v>
+        <v>220102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2902,10 +2893,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491996</v>
+        <v>491933</v>
       </c>
       <c r="R19" t="n">
-        <v>7024788</v>
+        <v>7024735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2940,11 +2931,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2974,16 +2960,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152674</v>
+        <v>135152646</v>
       </c>
       <c r="B20" t="n">
-        <v>99291</v>
+        <v>106391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2991,28 +2977,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3023,10 +3009,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491994</v>
+        <v>491996</v>
       </c>
       <c r="R20" t="n">
-        <v>7024761</v>
+        <v>7024788</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3061,6 +3047,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3090,16 +3081,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152795</v>
+        <v>135152674</v>
       </c>
       <c r="B21" t="n">
-        <v>101478</v>
+        <v>99291</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3107,21 +3098,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3139,10 +3130,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>492072</v>
+        <v>491994</v>
       </c>
       <c r="R21" t="n">
-        <v>7024744</v>
+        <v>7024761</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3206,13 +3197,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152799</v>
+        <v>135152795</v>
       </c>
       <c r="B22" t="n">
         <v>101478</v>
@@ -3255,10 +3246,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491940</v>
+        <v>492072</v>
       </c>
       <c r="R22" t="n">
-        <v>7024802</v>
+        <v>7024744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3322,13 +3313,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152803</v>
+        <v>135152799</v>
       </c>
       <c r="B23" t="n">
         <v>101478</v>
@@ -3371,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492030</v>
+        <v>491940</v>
       </c>
       <c r="R23" t="n">
-        <v>7024798</v>
+        <v>7024802</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3438,13 +3429,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152814</v>
+        <v>135152803</v>
       </c>
       <c r="B24" t="n">
         <v>101478</v>
@@ -3487,10 +3478,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492106</v>
+        <v>492030</v>
       </c>
       <c r="R24" t="n">
-        <v>7024668</v>
+        <v>7024798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3554,16 +3545,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152780</v>
+        <v>135152814</v>
       </c>
       <c r="B25" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3571,21 +3562,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3603,10 +3594,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492108</v>
+        <v>492106</v>
       </c>
       <c r="R25" t="n">
-        <v>7024715</v>
+        <v>7024668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3641,11 +3632,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3658,7 +3644,7 @@
       </c>
       <c r="AH25" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3675,13 +3661,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152781</v>
+        <v>135152780</v>
       </c>
       <c r="B26" t="n">
         <v>98285</v>
@@ -3724,10 +3710,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>491956</v>
+        <v>492108</v>
       </c>
       <c r="R26" t="n">
-        <v>7024753</v>
+        <v>7024715</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3762,6 +3748,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3774,12 +3765,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3796,13 +3782,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152782</v>
+        <v>135152781</v>
       </c>
       <c r="B27" t="n">
         <v>98285</v>
@@ -3845,7 +3831,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492020</v>
+        <v>491956</v>
       </c>
       <c r="R27" t="n">
         <v>7024753</v>
@@ -3917,13 +3903,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152783</v>
+        <v>135152782</v>
       </c>
       <c r="B28" t="n">
         <v>98285</v>
@@ -3966,10 +3952,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492059</v>
+        <v>492020</v>
       </c>
       <c r="R28" t="n">
-        <v>7024724</v>
+        <v>7024753</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4038,16 +4024,16 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152665</v>
+        <v>135152783</v>
       </c>
       <c r="B29" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4055,28 +4041,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -4087,10 +4073,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492004</v>
+        <v>492059</v>
       </c>
       <c r="R29" t="n">
-        <v>7024816</v>
+        <v>7024724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4137,7 +4123,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -4159,16 +4145,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152666</v>
+        <v>135471205</v>
       </c>
       <c r="B30" t="n">
-        <v>101380</v>
+        <v>98290</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4176,42 +4162,50 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491958</v>
+        <v>492009</v>
       </c>
       <c r="R30" t="n">
-        <v>7024801</v>
+        <v>7024701</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4238,12 +4232,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4256,35 +4250,30 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152684</v>
+        <v>135152665</v>
       </c>
       <c r="B31" t="n">
-        <v>99075</v>
+        <v>101380</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4292,16 +4281,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223049</v>
+        <v>222771</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4324,10 +4313,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492050</v>
+        <v>492004</v>
       </c>
       <c r="R31" t="n">
-        <v>7024700</v>
+        <v>7024816</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4374,7 +4363,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4391,16 +4385,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135152685</v>
+        <v>135152666</v>
       </c>
       <c r="B32" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4408,28 +4402,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -4440,10 +4434,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492048</v>
+        <v>491958</v>
       </c>
       <c r="R32" t="n">
-        <v>7024654</v>
+        <v>7024801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4507,16 +4501,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152693</v>
+        <v>135152684</v>
       </c>
       <c r="B33" t="n">
-        <v>101368</v>
+        <v>99075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4524,28 +4518,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>224885</v>
+        <v>223049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4556,10 +4550,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492089</v>
+        <v>492050</v>
       </c>
       <c r="R33" t="n">
-        <v>7024769</v>
+        <v>7024700</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4606,7 +4600,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4623,13 +4617,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152706</v>
+        <v>135152685</v>
       </c>
       <c r="B34" t="n">
         <v>101368</v>
@@ -4661,7 +4655,7 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4672,10 +4666,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491979</v>
+        <v>492048</v>
       </c>
       <c r="R34" t="n">
-        <v>7024678</v>
+        <v>7024654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4738,6 +4732,238 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -4778,6 +5004,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -2393,7 +2393,7 @@
         <v>135471439</v>
       </c>
       <c r="B15" t="n">
-        <v>98295</v>
+        <v>98297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>135471205</v>
       </c>
       <c r="B30" t="n">
-        <v>98290</v>
+        <v>98292</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152661</v>
+        <v>135152676</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>58415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491961</v>
+        <v>491978</v>
       </c>
       <c r="R11" t="n">
-        <v>7024767</v>
+        <v>7024717</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1965,11 +1965,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1982,11 +1977,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2003,67 +1993,59 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152663</v>
+        <v>135152777</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>99186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492035</v>
+        <v>492109</v>
       </c>
       <c r="R12" t="n">
-        <v>7024713</v>
+        <v>7024714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2100,7 +2082,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Flera plantor i blom i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2109,17 +2091,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2136,74 +2114,58 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135152676</v>
+        <v>135471439</v>
       </c>
       <c r="B13" t="n">
-        <v>58415</v>
+        <v>98297</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103001</v>
+        <v>219815</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491978</v>
+        <v>491957</v>
       </c>
       <c r="R13" t="n">
-        <v>7024717</v>
+        <v>7024690</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2227,12 +2189,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2241,38 +2203,34 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152777</v>
+        <v>135152656</v>
       </c>
       <c r="B14" t="n">
-        <v>99186</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2280,21 +2238,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2315,7 +2273,7 @@
         <v>492109</v>
       </c>
       <c r="R14" t="n">
-        <v>7024714</v>
+        <v>7024713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2352,7 +2310,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2384,16 +2342,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135471439</v>
+        <v>135152736</v>
       </c>
       <c r="B15" t="n">
-        <v>98297</v>
+        <v>99607</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2401,41 +2359,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219815</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491957</v>
+        <v>492090</v>
       </c>
       <c r="R15" t="n">
-        <v>7024690</v>
+        <v>7024764</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2459,12 +2421,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2477,30 +2439,35 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152656</v>
+        <v>135152787</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>108287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2508,28 +2475,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2540,10 +2507,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492109</v>
+        <v>492029</v>
       </c>
       <c r="R16" t="n">
-        <v>7024713</v>
+        <v>7024730</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2578,11 +2545,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2595,7 +2557,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2612,16 +2574,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135152736</v>
+        <v>135152735</v>
       </c>
       <c r="B17" t="n">
-        <v>99607</v>
+        <v>108357</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2629,28 +2591,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2661,10 +2623,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492090</v>
+        <v>491933</v>
       </c>
       <c r="R17" t="n">
-        <v>7024764</v>
+        <v>7024735</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2728,16 +2690,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152787</v>
+        <v>135152646</v>
       </c>
       <c r="B18" t="n">
-        <v>108287</v>
+        <v>106391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2745,28 +2707,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220083</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2777,10 +2739,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492029</v>
+        <v>491996</v>
       </c>
       <c r="R18" t="n">
-        <v>7024730</v>
+        <v>7024788</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2815,6 +2777,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2844,16 +2811,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152735</v>
+        <v>135152674</v>
       </c>
       <c r="B19" t="n">
-        <v>108357</v>
+        <v>99291</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,28 +2828,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220102</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2893,10 +2860,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491933</v>
+        <v>491994</v>
       </c>
       <c r="R19" t="n">
-        <v>7024735</v>
+        <v>7024761</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2960,16 +2927,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152646</v>
+        <v>135152795</v>
       </c>
       <c r="B20" t="n">
-        <v>106391</v>
+        <v>101478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2977,28 +2944,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3009,10 +2976,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491996</v>
+        <v>492072</v>
       </c>
       <c r="R20" t="n">
-        <v>7024788</v>
+        <v>7024744</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3047,11 +3014,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3081,16 +3043,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152674</v>
+        <v>135152799</v>
       </c>
       <c r="B21" t="n">
-        <v>99291</v>
+        <v>101478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3098,21 +3060,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3130,10 +3092,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491994</v>
+        <v>491940</v>
       </c>
       <c r="R21" t="n">
-        <v>7024761</v>
+        <v>7024802</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3197,13 +3159,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152795</v>
+        <v>135152803</v>
       </c>
       <c r="B22" t="n">
         <v>101478</v>
@@ -3246,10 +3208,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492072</v>
+        <v>492030</v>
       </c>
       <c r="R22" t="n">
-        <v>7024744</v>
+        <v>7024798</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3313,13 +3275,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152799</v>
+        <v>135152814</v>
       </c>
       <c r="B23" t="n">
         <v>101478</v>
@@ -3362,10 +3324,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491940</v>
+        <v>492106</v>
       </c>
       <c r="R23" t="n">
-        <v>7024802</v>
+        <v>7024668</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3429,16 +3391,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152803</v>
+        <v>135152780</v>
       </c>
       <c r="B24" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3446,21 +3408,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3478,10 +3440,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492030</v>
+        <v>492108</v>
       </c>
       <c r="R24" t="n">
-        <v>7024798</v>
+        <v>7024715</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3516,6 +3478,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3528,7 +3495,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3545,16 +3512,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152814</v>
+        <v>135152781</v>
       </c>
       <c r="B25" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3562,21 +3529,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3594,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492106</v>
+        <v>491956</v>
       </c>
       <c r="R25" t="n">
-        <v>7024668</v>
+        <v>7024753</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3647,6 +3614,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3661,13 +3633,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152780</v>
+        <v>135152782</v>
       </c>
       <c r="B26" t="n">
         <v>98285</v>
@@ -3710,10 +3682,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492108</v>
+        <v>492020</v>
       </c>
       <c r="R26" t="n">
-        <v>7024715</v>
+        <v>7024753</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3748,11 +3720,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3765,7 +3732,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3782,13 +3754,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152781</v>
+        <v>135152783</v>
       </c>
       <c r="B27" t="n">
         <v>98285</v>
@@ -3831,10 +3803,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491956</v>
+        <v>492059</v>
       </c>
       <c r="R27" t="n">
-        <v>7024753</v>
+        <v>7024724</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3903,16 +3875,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152782</v>
+        <v>135471205</v>
       </c>
       <c r="B28" t="n">
-        <v>98285</v>
+        <v>98292</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3937,8 +3909,16 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3948,14 +3928,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492020</v>
+        <v>492009</v>
       </c>
       <c r="R28" t="n">
-        <v>7024753</v>
+        <v>7024701</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3982,12 +3962,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4000,40 +3980,30 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152783</v>
+        <v>135152665</v>
       </c>
       <c r="B29" t="n">
-        <v>98285</v>
+        <v>101380</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4041,28 +4011,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -4073,10 +4043,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492059</v>
+        <v>492004</v>
       </c>
       <c r="R29" t="n">
-        <v>7024724</v>
+        <v>7024816</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4123,7 +4093,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -4145,16 +4115,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135471205</v>
+        <v>135152666</v>
       </c>
       <c r="B30" t="n">
-        <v>98292</v>
+        <v>101380</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4162,50 +4132,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492009</v>
+        <v>491958</v>
       </c>
       <c r="R30" t="n">
-        <v>7024701</v>
+        <v>7024801</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4232,12 +4194,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4250,30 +4212,35 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152665</v>
+        <v>135152684</v>
       </c>
       <c r="B31" t="n">
-        <v>101380</v>
+        <v>99075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4281,16 +4248,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>223049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4313,10 +4280,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492004</v>
+        <v>492050</v>
       </c>
       <c r="R31" t="n">
-        <v>7024816</v>
+        <v>7024700</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,12 +4330,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4385,16 +4347,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135152666</v>
+        <v>135152685</v>
       </c>
       <c r="B32" t="n">
-        <v>101380</v>
+        <v>101368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4402,28 +4364,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222771</v>
+        <v>224885</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -4434,10 +4396,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491958</v>
+        <v>492048</v>
       </c>
       <c r="R32" t="n">
-        <v>7024801</v>
+        <v>7024654</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4501,16 +4463,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135152685</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152684</v>
+        <v>135152693</v>
       </c>
       <c r="B33" t="n">
-        <v>99075</v>
+        <v>101368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4518,28 +4480,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223049</v>
+        <v>224885</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4550,10 +4512,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492050</v>
+        <v>492089</v>
       </c>
       <c r="R33" t="n">
-        <v>7024700</v>
+        <v>7024769</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4600,7 +4562,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4617,13 +4579,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152693</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152685</v>
+        <v>135152706</v>
       </c>
       <c r="B34" t="n">
         <v>101368</v>
@@ -4655,7 +4617,7 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4666,10 +4628,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492048</v>
+        <v>491979</v>
       </c>
       <c r="R34" t="n">
-        <v>7024654</v>
+        <v>7024678</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4732,238 +4694,6 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>135152693</v>
-      </c>
-      <c r="B35" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>492089</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7024769</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135152706</v>
-      </c>
-      <c r="B36" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>491979</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7024678</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5004,8 +4734,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152676</v>
+        <v>135152661</v>
       </c>
       <c r="B11" t="n">
-        <v>58415</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491978</v>
+        <v>491961</v>
       </c>
       <c r="R11" t="n">
-        <v>7024717</v>
+        <v>7024767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1965,6 +1965,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1977,6 +1982,11 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1993,59 +2003,67 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152777</v>
+        <v>135152663</v>
       </c>
       <c r="B12" t="n">
-        <v>99186</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492109</v>
+        <v>492035</v>
       </c>
       <c r="R12" t="n">
-        <v>7024714</v>
+        <v>7024713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2082,7 +2100,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2091,13 +2109,17 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2114,58 +2136,74 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135471439</v>
+        <v>135152676</v>
       </c>
       <c r="B13" t="n">
-        <v>98297</v>
+        <v>58415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219815</v>
+        <v>103001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491957</v>
+        <v>491978</v>
       </c>
       <c r="R13" t="n">
-        <v>7024690</v>
+        <v>7024717</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2189,12 +2227,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2203,34 +2241,38 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152656</v>
+        <v>135152777</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,21 +2280,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2273,7 +2315,7 @@
         <v>492109</v>
       </c>
       <c r="R14" t="n">
-        <v>7024713</v>
+        <v>7024714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2310,7 +2352,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>Flera plantor i blom i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,16 +2384,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135152736</v>
+        <v>135471439</v>
       </c>
       <c r="B15" t="n">
-        <v>99607</v>
+        <v>98297</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2359,45 +2401,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>219815</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492090</v>
+        <v>491957</v>
       </c>
       <c r="R15" t="n">
-        <v>7024764</v>
+        <v>7024690</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2421,12 +2459,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2439,35 +2477,30 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152787</v>
+        <v>135152656</v>
       </c>
       <c r="B16" t="n">
-        <v>108287</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,28 +2508,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220083</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2507,10 +2540,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492029</v>
+        <v>492109</v>
       </c>
       <c r="R16" t="n">
-        <v>7024730</v>
+        <v>7024713</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2545,6 +2578,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2557,7 +2595,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2574,16 +2612,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135152735</v>
+        <v>135152736</v>
       </c>
       <c r="B17" t="n">
-        <v>108357</v>
+        <v>99607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2591,28 +2629,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2623,10 +2661,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491933</v>
+        <v>492090</v>
       </c>
       <c r="R17" t="n">
-        <v>7024735</v>
+        <v>7024764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2690,16 +2728,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152646</v>
+        <v>135152787</v>
       </c>
       <c r="B18" t="n">
-        <v>106391</v>
+        <v>108287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,28 +2745,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>220083</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2739,10 +2777,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491996</v>
+        <v>492029</v>
       </c>
       <c r="R18" t="n">
-        <v>7024788</v>
+        <v>7024730</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2777,11 +2815,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2811,16 +2844,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152674</v>
+        <v>135152735</v>
       </c>
       <c r="B19" t="n">
-        <v>99291</v>
+        <v>108357</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2828,28 +2861,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>220102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2860,10 +2893,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491994</v>
+        <v>491933</v>
       </c>
       <c r="R19" t="n">
-        <v>7024761</v>
+        <v>7024735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2927,16 +2960,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152795</v>
+        <v>135152646</v>
       </c>
       <c r="B20" t="n">
-        <v>101478</v>
+        <v>106391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2944,28 +2977,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -2976,10 +3009,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492072</v>
+        <v>491996</v>
       </c>
       <c r="R20" t="n">
-        <v>7024744</v>
+        <v>7024788</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3014,6 +3047,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3043,16 +3081,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152799</v>
+        <v>135152674</v>
       </c>
       <c r="B21" t="n">
-        <v>101478</v>
+        <v>99291</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3060,21 +3098,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3092,10 +3130,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491940</v>
+        <v>491994</v>
       </c>
       <c r="R21" t="n">
-        <v>7024802</v>
+        <v>7024761</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3159,13 +3197,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152803</v>
+        <v>135152795</v>
       </c>
       <c r="B22" t="n">
         <v>101478</v>
@@ -3208,10 +3246,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492030</v>
+        <v>492072</v>
       </c>
       <c r="R22" t="n">
-        <v>7024798</v>
+        <v>7024744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3275,13 +3313,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152814</v>
+        <v>135152799</v>
       </c>
       <c r="B23" t="n">
         <v>101478</v>
@@ -3324,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492106</v>
+        <v>491940</v>
       </c>
       <c r="R23" t="n">
-        <v>7024668</v>
+        <v>7024802</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3391,16 +3429,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152780</v>
+        <v>135152803</v>
       </c>
       <c r="B24" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3408,21 +3446,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3440,10 +3478,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492108</v>
+        <v>492030</v>
       </c>
       <c r="R24" t="n">
-        <v>7024715</v>
+        <v>7024798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3478,11 +3516,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3495,7 +3528,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3512,16 +3545,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152781</v>
+        <v>135152814</v>
       </c>
       <c r="B25" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3529,21 +3562,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3561,10 +3594,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491956</v>
+        <v>492106</v>
       </c>
       <c r="R25" t="n">
-        <v>7024753</v>
+        <v>7024668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3614,11 +3647,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3633,13 +3661,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152782</v>
+        <v>135152780</v>
       </c>
       <c r="B26" t="n">
         <v>98285</v>
@@ -3682,10 +3710,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492020</v>
+        <v>492108</v>
       </c>
       <c r="R26" t="n">
-        <v>7024753</v>
+        <v>7024715</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3720,6 +3748,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3732,12 +3765,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3754,13 +3782,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152783</v>
+        <v>135152781</v>
       </c>
       <c r="B27" t="n">
         <v>98285</v>
@@ -3803,10 +3831,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492059</v>
+        <v>491956</v>
       </c>
       <c r="R27" t="n">
-        <v>7024724</v>
+        <v>7024753</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3875,16 +3903,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135471205</v>
+        <v>135152782</v>
       </c>
       <c r="B28" t="n">
-        <v>98292</v>
+        <v>98285</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3909,16 +3937,8 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3928,14 +3948,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492009</v>
+        <v>492020</v>
       </c>
       <c r="R28" t="n">
-        <v>7024701</v>
+        <v>7024753</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3962,12 +3982,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3980,30 +4000,40 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152665</v>
+        <v>135152783</v>
       </c>
       <c r="B29" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4011,28 +4041,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -4043,10 +4073,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492004</v>
+        <v>492059</v>
       </c>
       <c r="R29" t="n">
-        <v>7024816</v>
+        <v>7024724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4093,7 +4123,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -4115,16 +4145,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152666</v>
+        <v>135471205</v>
       </c>
       <c r="B30" t="n">
-        <v>101380</v>
+        <v>98292</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4132,42 +4162,50 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491958</v>
+        <v>492009</v>
       </c>
       <c r="R30" t="n">
-        <v>7024801</v>
+        <v>7024701</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4194,12 +4232,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4212,35 +4250,30 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152684</v>
+        <v>135152665</v>
       </c>
       <c r="B31" t="n">
-        <v>99075</v>
+        <v>101380</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4248,16 +4281,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223049</v>
+        <v>222771</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4280,10 +4313,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492050</v>
+        <v>492004</v>
       </c>
       <c r="R31" t="n">
-        <v>7024700</v>
+        <v>7024816</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4330,7 +4363,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4347,16 +4385,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135152685</v>
+        <v>135152666</v>
       </c>
       <c r="B32" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4364,28 +4402,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -4396,10 +4434,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492048</v>
+        <v>491958</v>
       </c>
       <c r="R32" t="n">
-        <v>7024654</v>
+        <v>7024801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4463,16 +4501,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152693</v>
+        <v>135152684</v>
       </c>
       <c r="B33" t="n">
-        <v>101368</v>
+        <v>99075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4480,28 +4518,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>224885</v>
+        <v>223049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4512,10 +4550,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492089</v>
+        <v>492050</v>
       </c>
       <c r="R33" t="n">
-        <v>7024769</v>
+        <v>7024700</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4562,7 +4600,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4579,13 +4617,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152706</v>
+        <v>135152685</v>
       </c>
       <c r="B34" t="n">
         <v>101368</v>
@@ -4617,7 +4655,7 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4628,10 +4666,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491979</v>
+        <v>492048</v>
       </c>
       <c r="R34" t="n">
-        <v>7024678</v>
+        <v>7024654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4694,6 +4732,238 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -4734,6 +5004,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -1875,7 +1875,7 @@
         <v>135152661</v>
       </c>
       <c r="B11" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
         <v>135152663</v>
       </c>
       <c r="B12" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>135471439</v>
       </c>
       <c r="B15" t="n">
-        <v>98297</v>
+        <v>98314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -4154,7 +4154,7 @@
         <v>135471205</v>
       </c>
       <c r="B30" t="n">
-        <v>98292</v>
+        <v>98309</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152661</v>
+        <v>135152676</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>58415</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491961</v>
+        <v>491978</v>
       </c>
       <c r="R11" t="n">
-        <v>7024767</v>
+        <v>7024717</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1965,11 +1965,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1982,11 +1977,6 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2003,67 +1993,59 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152663</v>
+        <v>135152777</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>99186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>219790</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492035</v>
+        <v>492109</v>
       </c>
       <c r="R12" t="n">
-        <v>7024713</v>
+        <v>7024714</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2100,7 +2082,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Flera plantor i blom i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2109,17 +2091,13 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2136,74 +2114,58 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135152676</v>
+        <v>135471439</v>
       </c>
       <c r="B13" t="n">
-        <v>58415</v>
+        <v>98314</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103001</v>
+        <v>219815</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491978</v>
+        <v>491957</v>
       </c>
       <c r="R13" t="n">
-        <v>7024717</v>
+        <v>7024690</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2227,12 +2189,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2241,38 +2203,34 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152777</v>
+        <v>135152656</v>
       </c>
       <c r="B14" t="n">
-        <v>99186</v>
+        <v>99293</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2280,21 +2238,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2315,7 +2273,7 @@
         <v>492109</v>
       </c>
       <c r="R14" t="n">
-        <v>7024714</v>
+        <v>7024713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2352,7 +2310,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2384,16 +2342,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135471439</v>
+        <v>135152736</v>
       </c>
       <c r="B15" t="n">
-        <v>98314</v>
+        <v>99607</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2401,41 +2359,45 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219815</v>
+        <v>219880</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491957</v>
+        <v>492090</v>
       </c>
       <c r="R15" t="n">
-        <v>7024690</v>
+        <v>7024764</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2459,12 +2421,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2477,30 +2439,35 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152656</v>
+        <v>135152787</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>108287</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2508,28 +2475,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2540,10 +2507,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492109</v>
+        <v>492029</v>
       </c>
       <c r="R16" t="n">
-        <v>7024713</v>
+        <v>7024730</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2578,11 +2545,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2595,7 +2557,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2612,16 +2574,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135152736</v>
+        <v>135152735</v>
       </c>
       <c r="B17" t="n">
-        <v>99607</v>
+        <v>108357</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2629,28 +2591,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2661,10 +2623,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492090</v>
+        <v>491933</v>
       </c>
       <c r="R17" t="n">
-        <v>7024764</v>
+        <v>7024735</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2728,16 +2690,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152787</v>
+        <v>135152646</v>
       </c>
       <c r="B18" t="n">
-        <v>108287</v>
+        <v>106391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2745,28 +2707,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220083</v>
+        <v>221725</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2777,10 +2739,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492029</v>
+        <v>491996</v>
       </c>
       <c r="R18" t="n">
-        <v>7024730</v>
+        <v>7024788</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2815,6 +2777,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2844,16 +2811,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152735</v>
+        <v>135152674</v>
       </c>
       <c r="B19" t="n">
-        <v>108357</v>
+        <v>99291</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,28 +2828,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220102</v>
+        <v>221952</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2893,10 +2860,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491933</v>
+        <v>491994</v>
       </c>
       <c r="R19" t="n">
-        <v>7024735</v>
+        <v>7024761</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2960,16 +2927,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152646</v>
+        <v>135152795</v>
       </c>
       <c r="B20" t="n">
-        <v>106391</v>
+        <v>101478</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2977,28 +2944,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3009,10 +2976,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491996</v>
+        <v>492072</v>
       </c>
       <c r="R20" t="n">
-        <v>7024788</v>
+        <v>7024744</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3047,11 +3014,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3081,16 +3043,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152674</v>
+        <v>135152799</v>
       </c>
       <c r="B21" t="n">
-        <v>99291</v>
+        <v>101478</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3098,21 +3060,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3130,10 +3092,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491994</v>
+        <v>491940</v>
       </c>
       <c r="R21" t="n">
-        <v>7024761</v>
+        <v>7024802</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3197,13 +3159,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152795</v>
+        <v>135152803</v>
       </c>
       <c r="B22" t="n">
         <v>101478</v>
@@ -3246,10 +3208,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492072</v>
+        <v>492030</v>
       </c>
       <c r="R22" t="n">
-        <v>7024744</v>
+        <v>7024798</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3313,13 +3275,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152799</v>
+        <v>135152814</v>
       </c>
       <c r="B23" t="n">
         <v>101478</v>
@@ -3362,10 +3324,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491940</v>
+        <v>492106</v>
       </c>
       <c r="R23" t="n">
-        <v>7024802</v>
+        <v>7024668</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3429,16 +3391,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152803</v>
+        <v>135152780</v>
       </c>
       <c r="B24" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3446,21 +3408,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3478,10 +3440,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492030</v>
+        <v>492108</v>
       </c>
       <c r="R24" t="n">
-        <v>7024798</v>
+        <v>7024715</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3516,6 +3478,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3528,7 +3495,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3545,16 +3512,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152814</v>
+        <v>135152781</v>
       </c>
       <c r="B25" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3562,21 +3529,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3594,10 +3561,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492106</v>
+        <v>491956</v>
       </c>
       <c r="R25" t="n">
-        <v>7024668</v>
+        <v>7024753</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3647,6 +3614,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3661,13 +3633,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152780</v>
+        <v>135152782</v>
       </c>
       <c r="B26" t="n">
         <v>98285</v>
@@ -3710,10 +3682,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492108</v>
+        <v>492020</v>
       </c>
       <c r="R26" t="n">
-        <v>7024715</v>
+        <v>7024753</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3748,11 +3720,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3765,7 +3732,12 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3782,13 +3754,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152781</v>
+        <v>135152783</v>
       </c>
       <c r="B27" t="n">
         <v>98285</v>
@@ -3831,10 +3803,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491956</v>
+        <v>492059</v>
       </c>
       <c r="R27" t="n">
-        <v>7024753</v>
+        <v>7024724</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3903,16 +3875,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152782</v>
+        <v>135471205</v>
       </c>
       <c r="B28" t="n">
-        <v>98285</v>
+        <v>98309</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3937,8 +3909,16 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3948,14 +3928,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492020</v>
+        <v>492009</v>
       </c>
       <c r="R28" t="n">
-        <v>7024753</v>
+        <v>7024701</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3982,12 +3962,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4000,40 +3980,30 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152783</v>
+        <v>135152665</v>
       </c>
       <c r="B29" t="n">
-        <v>98285</v>
+        <v>101380</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4041,28 +4011,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -4073,10 +4043,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492059</v>
+        <v>492004</v>
       </c>
       <c r="R29" t="n">
-        <v>7024724</v>
+        <v>7024816</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4123,7 +4093,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -4145,16 +4115,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135471205</v>
+        <v>135152666</v>
       </c>
       <c r="B30" t="n">
-        <v>98309</v>
+        <v>101380</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4162,50 +4132,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492009</v>
+        <v>491958</v>
       </c>
       <c r="R30" t="n">
-        <v>7024701</v>
+        <v>7024801</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4232,12 +4194,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4250,30 +4212,35 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152665</v>
+        <v>135152684</v>
       </c>
       <c r="B31" t="n">
-        <v>101380</v>
+        <v>99075</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4281,16 +4248,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>223049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4313,10 +4280,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492004</v>
+        <v>492050</v>
       </c>
       <c r="R31" t="n">
-        <v>7024816</v>
+        <v>7024700</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,12 +4330,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI31" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4385,16 +4347,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135152666</v>
+        <v>135152685</v>
       </c>
       <c r="B32" t="n">
-        <v>101380</v>
+        <v>101368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4402,28 +4364,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222771</v>
+        <v>224885</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -4434,10 +4396,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491958</v>
+        <v>492048</v>
       </c>
       <c r="R32" t="n">
-        <v>7024801</v>
+        <v>7024654</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4501,16 +4463,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135152685</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152684</v>
+        <v>135152693</v>
       </c>
       <c r="B33" t="n">
-        <v>99075</v>
+        <v>101368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4518,28 +4480,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223049</v>
+        <v>224885</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4550,10 +4512,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492050</v>
+        <v>492089</v>
       </c>
       <c r="R33" t="n">
-        <v>7024700</v>
+        <v>7024769</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4600,7 +4562,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4617,13 +4579,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152693</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152685</v>
+        <v>135152706</v>
       </c>
       <c r="B34" t="n">
         <v>101368</v>
@@ -4655,7 +4617,7 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4666,10 +4628,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492048</v>
+        <v>491979</v>
       </c>
       <c r="R34" t="n">
-        <v>7024654</v>
+        <v>7024678</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4732,238 +4694,6 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>135152693</v>
-      </c>
-      <c r="B35" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q35" t="n">
-        <v>492089</v>
-      </c>
-      <c r="R35" t="n">
-        <v>7024769</v>
-      </c>
-      <c r="S35" t="n">
-        <v>10</v>
-      </c>
-      <c r="T35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V35" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>135152706</v>
-      </c>
-      <c r="B36" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>491979</v>
-      </c>
-      <c r="R36" t="n">
-        <v>7024678</v>
-      </c>
-      <c r="S36" t="n">
-        <v>10</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5004,8 +4734,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1872,10 +1872,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152676</v>
+        <v>135152661</v>
       </c>
       <c r="B11" t="n">
-        <v>58415</v>
+        <v>57982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1883,21 +1883,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1927,10 +1927,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491978</v>
+        <v>491961</v>
       </c>
       <c r="R11" t="n">
-        <v>7024717</v>
+        <v>7024767</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1965,6 +1965,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1977,6 +1982,11 @@
       <c r="AH11" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -1993,59 +2003,67 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152777</v>
+        <v>135152663</v>
       </c>
       <c r="B12" t="n">
-        <v>99186</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219790</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492109</v>
+        <v>492035</v>
       </c>
       <c r="R12" t="n">
-        <v>7024714</v>
+        <v>7024713</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2082,7 +2100,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2091,13 +2109,17 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2114,58 +2136,74 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135471439</v>
+        <v>135152676</v>
       </c>
       <c r="B13" t="n">
-        <v>98314</v>
+        <v>58415</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219815</v>
+        <v>103001</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491957</v>
+        <v>491978</v>
       </c>
       <c r="R13" t="n">
-        <v>7024690</v>
+        <v>7024717</v>
       </c>
       <c r="S13" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2189,12 +2227,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2203,34 +2241,38 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152656</v>
+        <v>135152777</v>
       </c>
       <c r="B14" t="n">
-        <v>99293</v>
+        <v>99186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2238,21 +2280,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2273,7 +2315,7 @@
         <v>492109</v>
       </c>
       <c r="R14" t="n">
-        <v>7024713</v>
+        <v>7024714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2310,7 +2352,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>Flera plantor i blom i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2342,16 +2384,16 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135152736</v>
+        <v>135471439</v>
       </c>
       <c r="B15" t="n">
-        <v>99607</v>
+        <v>98314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2359,45 +2401,41 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219880</v>
+        <v>219815</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492090</v>
+        <v>491957</v>
       </c>
       <c r="R15" t="n">
-        <v>7024764</v>
+        <v>7024690</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2421,12 +2459,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2439,35 +2477,30 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152787</v>
+        <v>135152656</v>
       </c>
       <c r="B16" t="n">
-        <v>108287</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2475,28 +2508,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220083</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
@@ -2507,10 +2540,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>492029</v>
+        <v>492109</v>
       </c>
       <c r="R16" t="n">
-        <v>7024730</v>
+        <v>7024713</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2545,6 +2578,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2557,7 +2595,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2574,16 +2612,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135152735</v>
+        <v>135152736</v>
       </c>
       <c r="B17" t="n">
-        <v>108357</v>
+        <v>99607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2591,28 +2629,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -2623,10 +2661,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491933</v>
+        <v>492090</v>
       </c>
       <c r="R17" t="n">
-        <v>7024735</v>
+        <v>7024764</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2690,16 +2728,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152646</v>
+        <v>135152787</v>
       </c>
       <c r="B18" t="n">
-        <v>106391</v>
+        <v>108287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2707,28 +2745,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221725</v>
+        <v>220083</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2739,10 +2777,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>491996</v>
+        <v>492029</v>
       </c>
       <c r="R18" t="n">
-        <v>7024788</v>
+        <v>7024730</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2777,11 +2815,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2811,16 +2844,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152674</v>
+        <v>135152735</v>
       </c>
       <c r="B19" t="n">
-        <v>99291</v>
+        <v>108357</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2828,28 +2861,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221952</v>
+        <v>220102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2860,10 +2893,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491994</v>
+        <v>491933</v>
       </c>
       <c r="R19" t="n">
-        <v>7024761</v>
+        <v>7024735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2927,16 +2960,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152795</v>
+        <v>135152646</v>
       </c>
       <c r="B20" t="n">
-        <v>101478</v>
+        <v>106391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2944,28 +2977,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -2976,10 +3009,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492072</v>
+        <v>491996</v>
       </c>
       <c r="R20" t="n">
-        <v>7024744</v>
+        <v>7024788</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3014,6 +3047,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3043,16 +3081,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152799</v>
+        <v>135152674</v>
       </c>
       <c r="B21" t="n">
-        <v>101478</v>
+        <v>99291</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3060,21 +3098,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3092,10 +3130,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491940</v>
+        <v>491994</v>
       </c>
       <c r="R21" t="n">
-        <v>7024802</v>
+        <v>7024761</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3159,13 +3197,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152803</v>
+        <v>135152795</v>
       </c>
       <c r="B22" t="n">
         <v>101478</v>
@@ -3208,10 +3246,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492030</v>
+        <v>492072</v>
       </c>
       <c r="R22" t="n">
-        <v>7024798</v>
+        <v>7024744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3275,13 +3313,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152814</v>
+        <v>135152799</v>
       </c>
       <c r="B23" t="n">
         <v>101478</v>
@@ -3324,10 +3362,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>492106</v>
+        <v>491940</v>
       </c>
       <c r="R23" t="n">
-        <v>7024668</v>
+        <v>7024802</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3391,16 +3429,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152780</v>
+        <v>135152803</v>
       </c>
       <c r="B24" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3408,21 +3446,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3440,10 +3478,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492108</v>
+        <v>492030</v>
       </c>
       <c r="R24" t="n">
-        <v>7024715</v>
+        <v>7024798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3478,11 +3516,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3495,7 +3528,7 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3512,16 +3545,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152781</v>
+        <v>135152814</v>
       </c>
       <c r="B25" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3529,21 +3562,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3561,10 +3594,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491956</v>
+        <v>492106</v>
       </c>
       <c r="R25" t="n">
-        <v>7024753</v>
+        <v>7024668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3614,11 +3647,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI25" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
@@ -3633,13 +3661,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152782</v>
+        <v>135152780</v>
       </c>
       <c r="B26" t="n">
         <v>98285</v>
@@ -3682,10 +3710,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492020</v>
+        <v>492108</v>
       </c>
       <c r="R26" t="n">
-        <v>7024753</v>
+        <v>7024715</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3720,6 +3748,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3732,12 +3765,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3754,13 +3782,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152783</v>
+        <v>135152781</v>
       </c>
       <c r="B27" t="n">
         <v>98285</v>
@@ -3803,10 +3831,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492059</v>
+        <v>491956</v>
       </c>
       <c r="R27" t="n">
-        <v>7024724</v>
+        <v>7024753</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3875,16 +3903,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135471205</v>
+        <v>135152782</v>
       </c>
       <c r="B28" t="n">
-        <v>98309</v>
+        <v>98285</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3909,16 +3937,8 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -3928,14 +3948,14 @@
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492009</v>
+        <v>492020</v>
       </c>
       <c r="R28" t="n">
-        <v>7024701</v>
+        <v>7024753</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3962,12 +3982,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3980,30 +4000,40 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152665</v>
+        <v>135152783</v>
       </c>
       <c r="B29" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4011,28 +4041,28 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
@@ -4043,10 +4073,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492004</v>
+        <v>492059</v>
       </c>
       <c r="R29" t="n">
-        <v>7024816</v>
+        <v>7024724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4093,7 +4123,7 @@
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -4115,16 +4145,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152666</v>
+        <v>135471205</v>
       </c>
       <c r="B30" t="n">
-        <v>101380</v>
+        <v>98309</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4132,42 +4162,50 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>491958</v>
+        <v>492009</v>
       </c>
       <c r="R30" t="n">
-        <v>7024801</v>
+        <v>7024701</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4194,12 +4232,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4212,35 +4250,30 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152684</v>
+        <v>135152665</v>
       </c>
       <c r="B31" t="n">
-        <v>99075</v>
+        <v>101380</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4248,16 +4281,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>223049</v>
+        <v>222771</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4280,10 +4313,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492050</v>
+        <v>492004</v>
       </c>
       <c r="R31" t="n">
-        <v>7024700</v>
+        <v>7024816</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4330,7 +4363,12 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4347,16 +4385,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135152685</v>
+        <v>135152666</v>
       </c>
       <c r="B32" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4364,28 +4402,28 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
@@ -4396,10 +4434,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492048</v>
+        <v>491958</v>
       </c>
       <c r="R32" t="n">
-        <v>7024654</v>
+        <v>7024801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4463,16 +4501,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152693</v>
+        <v>135152684</v>
       </c>
       <c r="B33" t="n">
-        <v>101368</v>
+        <v>99075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4480,28 +4518,28 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>224885</v>
+        <v>223049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
@@ -4512,10 +4550,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492089</v>
+        <v>492050</v>
       </c>
       <c r="R33" t="n">
-        <v>7024769</v>
+        <v>7024700</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4562,7 +4600,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4579,13 +4617,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152706</v>
+        <v>135152685</v>
       </c>
       <c r="B34" t="n">
         <v>101368</v>
@@ -4617,7 +4655,7 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4628,10 +4666,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491979</v>
+        <v>492048</v>
       </c>
       <c r="R34" t="n">
-        <v>7024678</v>
+        <v>7024654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4694,6 +4732,238 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B35" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -4734,6 +5004,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,49 +680,50 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>135152765</v>
+        <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>96481</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2812</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>492018</v>
+        <v>492064</v>
       </c>
       <c r="R2" t="n">
-        <v>7024683</v>
+        <v>7024653</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,13 +774,32 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -786,43 +816,44 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152765</t>
+          <t>https://artportalen.se/Sighting/136200752</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135152773</v>
+        <v>135152765</v>
       </c>
       <c r="B3" t="n">
-        <v>79438</v>
+        <v>96481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2812</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -830,10 +861,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>492104</v>
+        <v>492018</v>
       </c>
       <c r="R3" t="n">
-        <v>7024702</v>
+        <v>7024683</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -868,11 +899,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På en stående död gran.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,26 +914,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -922,13 +928,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152773</t>
+          <t>https://artportalen.se/Sighting/135152765</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135152774</v>
+        <v>135152773</v>
       </c>
       <c r="B4" t="n">
         <v>79438</v>
@@ -966,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>492073</v>
+        <v>492104</v>
       </c>
       <c r="R4" t="n">
-        <v>7024743</v>
+        <v>7024702</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1004,6 +1010,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en stående död gran.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1031,12 +1042,12 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1053,13 +1064,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152774</t>
+          <t>https://artportalen.se/Sighting/135152773</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135152775</v>
+        <v>135152774</v>
       </c>
       <c r="B5" t="n">
         <v>79438</v>
@@ -1097,10 +1108,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>492097</v>
+        <v>492073</v>
       </c>
       <c r="R5" t="n">
-        <v>7024693</v>
+        <v>7024743</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1184,38 +1195,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152775</t>
+          <t>https://artportalen.se/Sighting/135152774</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135152715</v>
+        <v>135152775</v>
       </c>
       <c r="B6" t="n">
-        <v>80553</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1228,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>492067</v>
+        <v>492097</v>
       </c>
       <c r="R6" t="n">
-        <v>7024791</v>
+        <v>7024693</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1266,11 +1277,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Enstaka bålar.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1288,22 +1294,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1320,13 +1326,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152715</t>
+          <t>https://artportalen.se/Sighting/135152775</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135152716</v>
+        <v>135152715</v>
       </c>
       <c r="B7" t="n">
         <v>80553</v>
@@ -1364,10 +1370,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>492005</v>
+        <v>492067</v>
       </c>
       <c r="R7" t="n">
-        <v>7024817</v>
+        <v>7024791</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1410,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en skadad levande sälg.</t>
+          <t>Enstaka bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1456,47 +1462,43 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152716</t>
+          <t>https://artportalen.se/Sighting/135152715</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135152672</v>
+        <v>135152716</v>
       </c>
       <c r="B8" t="n">
-        <v>80558</v>
+        <v>80553</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1504,10 +1506,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>491960</v>
+        <v>492005</v>
       </c>
       <c r="R8" t="n">
-        <v>7024789</v>
+        <v>7024817</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,7 +1546,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>På en smal rönn.</t>
+          <t>På en skadad levande sälg.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1564,12 +1566,12 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>rönn</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Sorbus aucuparia</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
@@ -1579,7 +1581,7 @@
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Sorbus aucuparia</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1596,13 +1598,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152672</t>
+          <t>https://artportalen.se/Sighting/135152716</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135152673</v>
+        <v>135152672</v>
       </c>
       <c r="B9" t="n">
         <v>80558</v>
@@ -1644,10 +1646,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>491956</v>
+        <v>491960</v>
       </c>
       <c r="R9" t="n">
-        <v>7024744</v>
+        <v>7024789</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1682,6 +1684,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På en smal rönn.</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1699,12 +1706,12 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
@@ -1714,7 +1721,7 @@
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1731,16 +1738,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152673</t>
+          <t>https://artportalen.se/Sighting/135152672</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135152722</v>
+        <v>135152673</v>
       </c>
       <c r="B10" t="n">
-        <v>80565</v>
+        <v>80558</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1748,21 +1755,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6464</v>
+        <v>6462</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1779,10 +1786,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>492095</v>
+        <v>491956</v>
       </c>
       <c r="R10" t="n">
-        <v>7024733</v>
+        <v>7024744</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1866,71 +1873,58 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152722</t>
+          <t>https://artportalen.se/Sighting/135152673</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135152661</v>
+        <v>135152722</v>
       </c>
       <c r="B11" t="n">
-        <v>57982</v>
+        <v>80565</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>491961</v>
+        <v>492095</v>
       </c>
       <c r="R11" t="n">
-        <v>7024767</v>
+        <v>7024733</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1965,17 +1959,13 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1984,9 +1974,24 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2003,13 +2008,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152722</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152663</v>
+        <v>135152661</v>
       </c>
       <c r="B12" t="n">
         <v>57982</v>
@@ -2043,10 +2048,14 @@
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2060,10 +2069,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>492035</v>
+        <v>491961</v>
       </c>
       <c r="R12" t="n">
-        <v>7024713</v>
+        <v>7024767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2100,7 +2109,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2119,7 +2128,7 @@
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2136,16 +2145,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135152676</v>
+        <v>135152663</v>
       </c>
       <c r="B13" t="n">
-        <v>58415</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2153,21 +2162,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2176,14 +2185,10 @@
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2197,10 +2202,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>491978</v>
+        <v>492035</v>
       </c>
       <c r="R13" t="n">
-        <v>7024717</v>
+        <v>7024713</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2235,6 +2240,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2247,6 +2257,11 @@
       <c r="AH13" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2263,59 +2278,71 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152777</v>
+        <v>135152676</v>
       </c>
       <c r="B14" t="n">
-        <v>99186</v>
+        <v>58415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492109</v>
+        <v>491978</v>
       </c>
       <c r="R14" t="n">
-        <v>7024714</v>
+        <v>7024717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2350,24 +2377,18 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2384,58 +2405,70 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135471439</v>
+        <v>136199553</v>
       </c>
       <c r="B15" t="n">
-        <v>98314</v>
+        <v>58143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219815</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491957</v>
+        <v>492073</v>
       </c>
       <c r="R15" t="n">
-        <v>7024690</v>
+        <v>7024775</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2459,12 +2492,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2473,34 +2521,38 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152656</v>
+        <v>135152777</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2508,21 +2560,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2543,7 +2595,7 @@
         <v>492109</v>
       </c>
       <c r="R16" t="n">
-        <v>7024713</v>
+        <v>7024714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2580,7 +2632,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>Flera plantor i blom i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2612,16 +2664,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135152736</v>
+        <v>135471439</v>
       </c>
       <c r="B17" t="n">
-        <v>99607</v>
+        <v>98314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2629,45 +2681,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>219815</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492090</v>
+        <v>491957</v>
       </c>
       <c r="R17" t="n">
-        <v>7024764</v>
+        <v>7024690</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2691,12 +2739,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2709,35 +2757,30 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152787</v>
+        <v>135152656</v>
       </c>
       <c r="B18" t="n">
-        <v>108287</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2745,28 +2788,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220083</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2777,10 +2820,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492029</v>
+        <v>492109</v>
       </c>
       <c r="R18" t="n">
-        <v>7024730</v>
+        <v>7024713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2815,6 +2858,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2827,7 +2875,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2844,16 +2892,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152735</v>
+        <v>135152736</v>
       </c>
       <c r="B19" t="n">
-        <v>108357</v>
+        <v>99607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2861,28 +2909,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2893,10 +2941,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491933</v>
+        <v>492090</v>
       </c>
       <c r="R19" t="n">
-        <v>7024735</v>
+        <v>7024764</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2960,16 +3008,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152646</v>
+        <v>135152787</v>
       </c>
       <c r="B20" t="n">
-        <v>106391</v>
+        <v>108287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2977,28 +3025,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>220083</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3009,10 +3057,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491996</v>
+        <v>492029</v>
       </c>
       <c r="R20" t="n">
-        <v>7024788</v>
+        <v>7024730</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3047,11 +3095,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3081,16 +3124,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152674</v>
+        <v>135152735</v>
       </c>
       <c r="B21" t="n">
-        <v>99291</v>
+        <v>108357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3098,28 +3141,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>220102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3130,10 +3173,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491994</v>
+        <v>491933</v>
       </c>
       <c r="R21" t="n">
-        <v>7024761</v>
+        <v>7024735</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3197,16 +3240,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152795</v>
+        <v>135152646</v>
       </c>
       <c r="B22" t="n">
-        <v>101478</v>
+        <v>106391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3214,28 +3257,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3246,10 +3289,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492072</v>
+        <v>491996</v>
       </c>
       <c r="R22" t="n">
-        <v>7024744</v>
+        <v>7024788</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3284,6 +3327,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3313,16 +3361,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152799</v>
+        <v>135152674</v>
       </c>
       <c r="B23" t="n">
-        <v>101478</v>
+        <v>99291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3330,21 +3378,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3362,10 +3410,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491940</v>
+        <v>491994</v>
       </c>
       <c r="R23" t="n">
-        <v>7024802</v>
+        <v>7024761</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3429,13 +3477,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152803</v>
+        <v>135152795</v>
       </c>
       <c r="B24" t="n">
         <v>101478</v>
@@ -3478,10 +3526,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492030</v>
+        <v>492072</v>
       </c>
       <c r="R24" t="n">
-        <v>7024798</v>
+        <v>7024744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3545,13 +3593,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152814</v>
+        <v>135152799</v>
       </c>
       <c r="B25" t="n">
         <v>101478</v>
@@ -3594,10 +3642,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492106</v>
+        <v>491940</v>
       </c>
       <c r="R25" t="n">
-        <v>7024668</v>
+        <v>7024802</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3661,16 +3709,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152780</v>
+        <v>135152803</v>
       </c>
       <c r="B26" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3678,21 +3726,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3710,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492108</v>
+        <v>492030</v>
       </c>
       <c r="R26" t="n">
-        <v>7024715</v>
+        <v>7024798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3748,11 +3796,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3765,7 +3808,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3782,16 +3825,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152781</v>
+        <v>135152814</v>
       </c>
       <c r="B27" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3799,21 +3842,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3831,10 +3874,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491956</v>
+        <v>492106</v>
       </c>
       <c r="R27" t="n">
-        <v>7024753</v>
+        <v>7024668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3884,11 +3927,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3903,13 +3941,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152782</v>
+        <v>135152780</v>
       </c>
       <c r="B28" t="n">
         <v>98285</v>
@@ -3952,10 +3990,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492020</v>
+        <v>492108</v>
       </c>
       <c r="R28" t="n">
-        <v>7024753</v>
+        <v>7024715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3990,6 +4028,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4002,12 +4045,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4024,13 +4062,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152783</v>
+        <v>135152781</v>
       </c>
       <c r="B29" t="n">
         <v>98285</v>
@@ -4073,10 +4111,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492059</v>
+        <v>491956</v>
       </c>
       <c r="R29" t="n">
-        <v>7024724</v>
+        <v>7024753</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4145,16 +4183,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135471205</v>
+        <v>135152782</v>
       </c>
       <c r="B30" t="n">
-        <v>98309</v>
+        <v>98285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4179,16 +4217,8 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4198,14 +4228,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492009</v>
+        <v>492020</v>
       </c>
       <c r="R30" t="n">
-        <v>7024701</v>
+        <v>7024753</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4232,12 +4262,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4250,30 +4280,40 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152665</v>
+        <v>135152783</v>
       </c>
       <c r="B31" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4281,28 +4321,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4313,10 +4353,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492004</v>
+        <v>492059</v>
       </c>
       <c r="R31" t="n">
-        <v>7024816</v>
+        <v>7024724</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4363,7 +4403,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -4385,16 +4425,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135152666</v>
+        <v>135471205</v>
       </c>
       <c r="B32" t="n">
-        <v>101380</v>
+        <v>98309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4402,42 +4442,50 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491958</v>
+        <v>492009</v>
       </c>
       <c r="R32" t="n">
-        <v>7024801</v>
+        <v>7024701</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4464,12 +4512,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4482,35 +4530,30 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152684</v>
+        <v>135152665</v>
       </c>
       <c r="B33" t="n">
-        <v>99075</v>
+        <v>101380</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4518,16 +4561,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223049</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4550,10 +4593,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492050</v>
+        <v>492004</v>
       </c>
       <c r="R33" t="n">
-        <v>7024700</v>
+        <v>7024816</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4600,7 +4643,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4617,16 +4665,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152685</v>
+        <v>135152666</v>
       </c>
       <c r="B34" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4634,28 +4682,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4666,10 +4714,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492048</v>
+        <v>491958</v>
       </c>
       <c r="R34" t="n">
-        <v>7024654</v>
+        <v>7024801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4733,16 +4781,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152693</v>
+        <v>135152684</v>
       </c>
       <c r="B35" t="n">
-        <v>101368</v>
+        <v>99075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4750,28 +4798,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>224885</v>
+        <v>223049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4782,10 +4830,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492089</v>
+        <v>492050</v>
       </c>
       <c r="R35" t="n">
-        <v>7024769</v>
+        <v>7024700</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4832,7 +4880,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4849,13 +4897,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152706</v>
+        <v>135152685</v>
       </c>
       <c r="B36" t="n">
         <v>101368</v>
@@ -4887,7 +4935,7 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4898,10 +4946,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491979</v>
+        <v>492048</v>
       </c>
       <c r="R36" t="n">
-        <v>7024678</v>
+        <v>7024654</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4964,6 +5012,238 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5006,6 +5286,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152661</v>
+        <v>135152676</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>58415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491961</v>
+        <v>491978</v>
       </c>
       <c r="R12" t="n">
-        <v>7024767</v>
+        <v>7024717</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,11 +2107,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2124,11 +2119,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2145,16 +2135,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135152663</v>
+        <v>136199553</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>58143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,21 +2152,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2188,7 +2178,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2198,17 +2188,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492035</v>
+        <v>492073</v>
       </c>
       <c r="R13" t="n">
-        <v>7024713</v>
+        <v>7024775</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2232,17 +2222,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2256,12 +2256,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,71 +2273,59 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152676</v>
+        <v>135152777</v>
       </c>
       <c r="B14" t="n">
-        <v>58415</v>
+        <v>99186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491978</v>
+        <v>492109</v>
       </c>
       <c r="R14" t="n">
-        <v>7024717</v>
+        <v>7024714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2377,18 +2360,24 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flera plantor i blom i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2405,70 +2394,58 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136199553</v>
+        <v>135471439</v>
       </c>
       <c r="B15" t="n">
-        <v>58143</v>
+        <v>98314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>219815</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492073</v>
+        <v>491957</v>
       </c>
       <c r="R15" t="n">
-        <v>7024775</v>
+        <v>7024690</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2492,27 +2469,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>19:38</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2521,38 +2483,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152777</v>
+        <v>135152656</v>
       </c>
       <c r="B16" t="n">
-        <v>99186</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2560,21 +2518,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2595,7 +2553,7 @@
         <v>492109</v>
       </c>
       <c r="R16" t="n">
-        <v>7024714</v>
+        <v>7024713</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2632,7 +2590,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2664,16 +2622,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135471439</v>
+        <v>135152736</v>
       </c>
       <c r="B17" t="n">
-        <v>98314</v>
+        <v>99607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2681,41 +2639,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219815</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491957</v>
+        <v>492090</v>
       </c>
       <c r="R17" t="n">
-        <v>7024690</v>
+        <v>7024764</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2739,12 +2701,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2757,30 +2719,35 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152656</v>
+        <v>135152787</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>108287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2788,28 +2755,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2820,10 +2787,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492109</v>
+        <v>492029</v>
       </c>
       <c r="R18" t="n">
-        <v>7024713</v>
+        <v>7024730</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2858,11 +2825,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2875,7 +2837,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2892,16 +2854,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152736</v>
+        <v>135152735</v>
       </c>
       <c r="B19" t="n">
-        <v>99607</v>
+        <v>108357</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2909,28 +2871,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2941,10 +2903,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492090</v>
+        <v>491933</v>
       </c>
       <c r="R19" t="n">
-        <v>7024764</v>
+        <v>7024735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3008,16 +2970,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152787</v>
+        <v>135152646</v>
       </c>
       <c r="B20" t="n">
-        <v>108287</v>
+        <v>106391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3025,28 +2987,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220083</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3057,10 +3019,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492029</v>
+        <v>491996</v>
       </c>
       <c r="R20" t="n">
-        <v>7024730</v>
+        <v>7024788</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3095,6 +3057,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3124,16 +3091,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152735</v>
+        <v>135152674</v>
       </c>
       <c r="B21" t="n">
-        <v>108357</v>
+        <v>99291</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3141,28 +3108,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3173,10 +3140,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491933</v>
+        <v>491994</v>
       </c>
       <c r="R21" t="n">
-        <v>7024735</v>
+        <v>7024761</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3240,16 +3207,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152646</v>
+        <v>135152795</v>
       </c>
       <c r="B22" t="n">
-        <v>106391</v>
+        <v>101478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3257,28 +3224,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3289,10 +3256,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491996</v>
+        <v>492072</v>
       </c>
       <c r="R22" t="n">
-        <v>7024788</v>
+        <v>7024744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3327,11 +3294,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3361,16 +3323,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152674</v>
+        <v>135152799</v>
       </c>
       <c r="B23" t="n">
-        <v>99291</v>
+        <v>101478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3378,21 +3340,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3410,10 +3372,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491994</v>
+        <v>491940</v>
       </c>
       <c r="R23" t="n">
-        <v>7024761</v>
+        <v>7024802</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3477,13 +3439,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152795</v>
+        <v>135152803</v>
       </c>
       <c r="B24" t="n">
         <v>101478</v>
@@ -3526,10 +3488,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492072</v>
+        <v>492030</v>
       </c>
       <c r="R24" t="n">
-        <v>7024744</v>
+        <v>7024798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3593,13 +3555,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152799</v>
+        <v>135152814</v>
       </c>
       <c r="B25" t="n">
         <v>101478</v>
@@ -3642,10 +3604,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491940</v>
+        <v>492106</v>
       </c>
       <c r="R25" t="n">
-        <v>7024802</v>
+        <v>7024668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,16 +3671,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152803</v>
+        <v>135152780</v>
       </c>
       <c r="B26" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,21 +3688,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3758,10 +3720,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>492108</v>
       </c>
       <c r="R26" t="n">
-        <v>7024798</v>
+        <v>7024715</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3796,6 +3758,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3808,7 +3775,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3825,16 +3792,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152814</v>
+        <v>135152781</v>
       </c>
       <c r="B27" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3842,21 +3809,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3874,10 +3841,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492106</v>
+        <v>491956</v>
       </c>
       <c r="R27" t="n">
-        <v>7024668</v>
+        <v>7024753</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3927,6 +3894,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3941,13 +3913,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152780</v>
+        <v>135152782</v>
       </c>
       <c r="B28" t="n">
         <v>98285</v>
@@ -3990,10 +3962,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492108</v>
+        <v>492020</v>
       </c>
       <c r="R28" t="n">
-        <v>7024715</v>
+        <v>7024753</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4028,11 +4000,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4012,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4062,13 +4034,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152781</v>
+        <v>135152783</v>
       </c>
       <c r="B29" t="n">
         <v>98285</v>
@@ -4111,10 +4083,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491956</v>
+        <v>492059</v>
       </c>
       <c r="R29" t="n">
-        <v>7024753</v>
+        <v>7024724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4183,16 +4155,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152782</v>
+        <v>135471205</v>
       </c>
       <c r="B30" t="n">
-        <v>98285</v>
+        <v>98309</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4217,8 +4189,16 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4228,14 +4208,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492020</v>
+        <v>492009</v>
       </c>
       <c r="R30" t="n">
-        <v>7024753</v>
+        <v>7024701</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4262,12 +4242,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4280,40 +4260,30 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152783</v>
+        <v>135152665</v>
       </c>
       <c r="B31" t="n">
-        <v>98285</v>
+        <v>101380</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,28 +4291,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4353,10 +4323,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492059</v>
+        <v>492004</v>
       </c>
       <c r="R31" t="n">
-        <v>7024724</v>
+        <v>7024816</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4403,7 +4373,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -4425,16 +4395,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135471205</v>
+        <v>135152666</v>
       </c>
       <c r="B32" t="n">
-        <v>98309</v>
+        <v>101380</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4442,50 +4412,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492009</v>
+        <v>491958</v>
       </c>
       <c r="R32" t="n">
-        <v>7024701</v>
+        <v>7024801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4512,12 +4474,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,30 +4492,35 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152665</v>
+        <v>135152684</v>
       </c>
       <c r="B33" t="n">
-        <v>101380</v>
+        <v>99075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4561,16 +4528,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>223049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4593,10 +4560,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492004</v>
+        <v>492050</v>
       </c>
       <c r="R33" t="n">
-        <v>7024816</v>
+        <v>7024700</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4643,12 +4610,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4665,16 +4627,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152666</v>
+        <v>135152685</v>
       </c>
       <c r="B34" t="n">
-        <v>101380</v>
+        <v>101368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4682,28 +4644,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>224885</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4714,10 +4676,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491958</v>
+        <v>492048</v>
       </c>
       <c r="R34" t="n">
-        <v>7024801</v>
+        <v>7024654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4781,16 +4743,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135152685</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152684</v>
+        <v>135152693</v>
       </c>
       <c r="B35" t="n">
-        <v>99075</v>
+        <v>101368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4798,28 +4760,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223049</v>
+        <v>224885</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4830,10 +4792,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492050</v>
+        <v>492089</v>
       </c>
       <c r="R35" t="n">
-        <v>7024700</v>
+        <v>7024769</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4880,7 +4842,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4897,13 +4859,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152693</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152685</v>
+        <v>135152706</v>
       </c>
       <c r="B36" t="n">
         <v>101368</v>
@@ -4935,7 +4897,7 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4946,10 +4908,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492048</v>
+        <v>491979</v>
       </c>
       <c r="R36" t="n">
-        <v>7024654</v>
+        <v>7024678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5012,238 +4974,6 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>135152693</v>
-      </c>
-      <c r="B37" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>492089</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7024769</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>135152706</v>
-      </c>
-      <c r="B38" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>491979</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7024678</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5286,8 +5016,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2014,10 +2014,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152676</v>
+        <v>135152661</v>
       </c>
       <c r="B12" t="n">
-        <v>58415</v>
+        <v>57982</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491978</v>
+        <v>491961</v>
       </c>
       <c r="R12" t="n">
-        <v>7024717</v>
+        <v>7024767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,6 +2107,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2119,6 +2124,11 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2135,16 +2145,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136199553</v>
+        <v>135152663</v>
       </c>
       <c r="B13" t="n">
-        <v>58143</v>
+        <v>57982</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2152,21 +2162,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2178,7 +2188,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2188,17 +2198,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492073</v>
+        <v>492035</v>
       </c>
       <c r="R13" t="n">
-        <v>7024775</v>
+        <v>7024713</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2222,27 +2232,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2256,7 +2256,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2273,59 +2278,71 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152777</v>
+        <v>135152676</v>
       </c>
       <c r="B14" t="n">
-        <v>99186</v>
+        <v>58415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492109</v>
+        <v>491978</v>
       </c>
       <c r="R14" t="n">
-        <v>7024714</v>
+        <v>7024717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2360,24 +2377,18 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2394,58 +2405,70 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135471439</v>
+        <v>136199553</v>
       </c>
       <c r="B15" t="n">
-        <v>98314</v>
+        <v>58143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219815</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491957</v>
+        <v>492073</v>
       </c>
       <c r="R15" t="n">
-        <v>7024690</v>
+        <v>7024775</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2469,12 +2492,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2483,34 +2521,38 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152656</v>
+        <v>135152777</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2518,21 +2560,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2553,7 +2595,7 @@
         <v>492109</v>
       </c>
       <c r="R16" t="n">
-        <v>7024713</v>
+        <v>7024714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2590,7 +2632,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>Flera plantor i blom i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2622,16 +2664,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135152736</v>
+        <v>135471439</v>
       </c>
       <c r="B17" t="n">
-        <v>99607</v>
+        <v>98314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2639,45 +2681,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>219815</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492090</v>
+        <v>491957</v>
       </c>
       <c r="R17" t="n">
-        <v>7024764</v>
+        <v>7024690</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2701,12 +2739,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2719,35 +2757,30 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152787</v>
+        <v>135152656</v>
       </c>
       <c r="B18" t="n">
-        <v>108287</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2755,28 +2788,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220083</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2787,10 +2820,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492029</v>
+        <v>492109</v>
       </c>
       <c r="R18" t="n">
-        <v>7024730</v>
+        <v>7024713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2825,6 +2858,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2837,7 +2875,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2854,16 +2892,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152735</v>
+        <v>135152736</v>
       </c>
       <c r="B19" t="n">
-        <v>108357</v>
+        <v>99607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2871,28 +2909,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2903,10 +2941,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491933</v>
+        <v>492090</v>
       </c>
       <c r="R19" t="n">
-        <v>7024735</v>
+        <v>7024764</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2970,16 +3008,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152646</v>
+        <v>135152787</v>
       </c>
       <c r="B20" t="n">
-        <v>106391</v>
+        <v>108287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2987,28 +3025,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>220083</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3019,10 +3057,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491996</v>
+        <v>492029</v>
       </c>
       <c r="R20" t="n">
-        <v>7024788</v>
+        <v>7024730</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3057,11 +3095,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3091,16 +3124,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152674</v>
+        <v>135152735</v>
       </c>
       <c r="B21" t="n">
-        <v>99291</v>
+        <v>108357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,28 +3141,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>220102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3140,10 +3173,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491994</v>
+        <v>491933</v>
       </c>
       <c r="R21" t="n">
-        <v>7024761</v>
+        <v>7024735</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3207,16 +3240,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152795</v>
+        <v>135152646</v>
       </c>
       <c r="B22" t="n">
-        <v>101478</v>
+        <v>106391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3224,28 +3257,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3256,10 +3289,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492072</v>
+        <v>491996</v>
       </c>
       <c r="R22" t="n">
-        <v>7024744</v>
+        <v>7024788</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3294,6 +3327,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3323,16 +3361,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152799</v>
+        <v>135152674</v>
       </c>
       <c r="B23" t="n">
-        <v>101478</v>
+        <v>99291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3340,21 +3378,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3372,10 +3410,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491940</v>
+        <v>491994</v>
       </c>
       <c r="R23" t="n">
-        <v>7024802</v>
+        <v>7024761</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3439,13 +3477,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152803</v>
+        <v>135152795</v>
       </c>
       <c r="B24" t="n">
         <v>101478</v>
@@ -3488,10 +3526,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492030</v>
+        <v>492072</v>
       </c>
       <c r="R24" t="n">
-        <v>7024798</v>
+        <v>7024744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3555,13 +3593,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152814</v>
+        <v>135152799</v>
       </c>
       <c r="B25" t="n">
         <v>101478</v>
@@ -3604,10 +3642,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492106</v>
+        <v>491940</v>
       </c>
       <c r="R25" t="n">
-        <v>7024668</v>
+        <v>7024802</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3671,16 +3709,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152780</v>
+        <v>135152803</v>
       </c>
       <c r="B26" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3688,21 +3726,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3720,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492108</v>
+        <v>492030</v>
       </c>
       <c r="R26" t="n">
-        <v>7024715</v>
+        <v>7024798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3758,11 +3796,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3775,7 +3808,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3792,16 +3825,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152781</v>
+        <v>135152814</v>
       </c>
       <c r="B27" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3809,21 +3842,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3841,10 +3874,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491956</v>
+        <v>492106</v>
       </c>
       <c r="R27" t="n">
-        <v>7024753</v>
+        <v>7024668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3894,11 +3927,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3913,13 +3941,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152782</v>
+        <v>135152780</v>
       </c>
       <c r="B28" t="n">
         <v>98285</v>
@@ -3962,10 +3990,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492020</v>
+        <v>492108</v>
       </c>
       <c r="R28" t="n">
-        <v>7024753</v>
+        <v>7024715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4000,6 +4028,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4012,12 +4045,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4034,13 +4062,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152783</v>
+        <v>135152781</v>
       </c>
       <c r="B29" t="n">
         <v>98285</v>
@@ -4083,10 +4111,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492059</v>
+        <v>491956</v>
       </c>
       <c r="R29" t="n">
-        <v>7024724</v>
+        <v>7024753</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4155,16 +4183,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135471205</v>
+        <v>135152782</v>
       </c>
       <c r="B30" t="n">
-        <v>98309</v>
+        <v>98285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4189,16 +4217,8 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4208,14 +4228,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492009</v>
+        <v>492020</v>
       </c>
       <c r="R30" t="n">
-        <v>7024701</v>
+        <v>7024753</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4242,12 +4262,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4260,30 +4280,40 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152665</v>
+        <v>135152783</v>
       </c>
       <c r="B31" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4291,28 +4321,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4323,10 +4353,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492004</v>
+        <v>492059</v>
       </c>
       <c r="R31" t="n">
-        <v>7024816</v>
+        <v>7024724</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4373,7 +4403,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -4395,16 +4425,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135152666</v>
+        <v>135471205</v>
       </c>
       <c r="B32" t="n">
-        <v>101380</v>
+        <v>98309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4412,42 +4442,50 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491958</v>
+        <v>492009</v>
       </c>
       <c r="R32" t="n">
-        <v>7024801</v>
+        <v>7024701</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4474,12 +4512,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4492,35 +4530,30 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152684</v>
+        <v>135152665</v>
       </c>
       <c r="B33" t="n">
-        <v>99075</v>
+        <v>101380</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4528,16 +4561,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223049</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4560,10 +4593,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492050</v>
+        <v>492004</v>
       </c>
       <c r="R33" t="n">
-        <v>7024700</v>
+        <v>7024816</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4610,7 +4643,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4627,16 +4665,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152685</v>
+        <v>135152666</v>
       </c>
       <c r="B34" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4644,28 +4682,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4676,10 +4714,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492048</v>
+        <v>491958</v>
       </c>
       <c r="R34" t="n">
-        <v>7024654</v>
+        <v>7024801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4743,16 +4781,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152693</v>
+        <v>135152684</v>
       </c>
       <c r="B35" t="n">
-        <v>101368</v>
+        <v>99075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4760,28 +4798,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>224885</v>
+        <v>223049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4792,10 +4830,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492089</v>
+        <v>492050</v>
       </c>
       <c r="R35" t="n">
-        <v>7024769</v>
+        <v>7024700</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4842,7 +4880,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4859,13 +4897,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152706</v>
+        <v>135152685</v>
       </c>
       <c r="B36" t="n">
         <v>101368</v>
@@ -4897,7 +4935,7 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4908,10 +4946,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491979</v>
+        <v>492048</v>
       </c>
       <c r="R36" t="n">
-        <v>7024678</v>
+        <v>7024654</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4974,6 +5012,238 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5016,6 +5286,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135152661</v>
       </c>
       <c r="B12" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>135152663</v>
       </c>
       <c r="B13" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136199553</v>
       </c>
       <c r="B15" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135152661</v>
       </c>
       <c r="B12" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>135152663</v>
       </c>
       <c r="B13" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136199553</v>
       </c>
       <c r="B15" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135152661</v>
       </c>
       <c r="B12" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>135152663</v>
       </c>
       <c r="B13" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136199553</v>
       </c>
       <c r="B15" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>135152661</v>
       </c>
       <c r="B12" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>135152663</v>
       </c>
       <c r="B13" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2414,7 +2414,7 @@
         <v>136199553</v>
       </c>
       <c r="B15" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2014,10 +2014,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152661</v>
+        <v>135152676</v>
       </c>
       <c r="B12" t="n">
-        <v>57993</v>
+        <v>58415</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>103001</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491961</v>
+        <v>491978</v>
       </c>
       <c r="R12" t="n">
-        <v>7024767</v>
+        <v>7024717</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,11 +2107,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2124,11 +2119,6 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2145,16 +2135,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152661</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135152663</v>
+        <v>136199553</v>
       </c>
       <c r="B13" t="n">
-        <v>57993</v>
+        <v>58167</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2162,21 +2152,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2188,7 +2178,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2198,17 +2188,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492035</v>
+        <v>492073</v>
       </c>
       <c r="R13" t="n">
-        <v>7024713</v>
+        <v>7024775</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2232,17 +2222,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2256,12 +2256,7 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2278,71 +2273,59 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152663</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152676</v>
+        <v>135152777</v>
       </c>
       <c r="B14" t="n">
-        <v>58415</v>
+        <v>99186</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103001</v>
+        <v>219790</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>491978</v>
+        <v>492109</v>
       </c>
       <c r="R14" t="n">
-        <v>7024717</v>
+        <v>7024714</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2377,18 +2360,24 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Flera plantor i blom i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2405,70 +2394,58 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136199553</v>
+        <v>135471439</v>
       </c>
       <c r="B15" t="n">
-        <v>58154</v>
+        <v>98314</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>219815</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Newman</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>492073</v>
+        <v>491957</v>
       </c>
       <c r="R15" t="n">
-        <v>7024775</v>
+        <v>7024690</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>100</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2492,27 +2469,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>19:38</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2521,38 +2483,34 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152777</v>
+        <v>135152656</v>
       </c>
       <c r="B16" t="n">
-        <v>99186</v>
+        <v>99293</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2560,21 +2518,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2595,7 +2553,7 @@
         <v>492109</v>
       </c>
       <c r="R16" t="n">
-        <v>7024714</v>
+        <v>7024713</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2632,7 +2590,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2664,16 +2622,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135471439</v>
+        <v>135152736</v>
       </c>
       <c r="B17" t="n">
-        <v>98314</v>
+        <v>99607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2681,41 +2639,45 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219815</v>
+        <v>219880</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>491957</v>
+        <v>492090</v>
       </c>
       <c r="R17" t="n">
-        <v>7024690</v>
+        <v>7024764</v>
       </c>
       <c r="S17" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2739,12 +2701,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2757,30 +2719,35 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152656</v>
+        <v>135152787</v>
       </c>
       <c r="B18" t="n">
-        <v>99293</v>
+        <v>108287</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2788,28 +2755,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>219847</v>
+        <v>220083</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2820,10 +2787,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492109</v>
+        <v>492029</v>
       </c>
       <c r="R18" t="n">
-        <v>7024713</v>
+        <v>7024730</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2858,11 +2825,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2875,7 +2837,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2892,16 +2854,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152736</v>
+        <v>135152735</v>
       </c>
       <c r="B19" t="n">
-        <v>99607</v>
+        <v>108357</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2909,28 +2871,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219880</v>
+        <v>220102</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2941,10 +2903,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>492090</v>
+        <v>491933</v>
       </c>
       <c r="R19" t="n">
-        <v>7024764</v>
+        <v>7024735</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -3008,16 +2970,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152787</v>
+        <v>135152646</v>
       </c>
       <c r="B20" t="n">
-        <v>108287</v>
+        <v>106391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3025,28 +2987,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220083</v>
+        <v>221725</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3057,10 +3019,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>492029</v>
+        <v>491996</v>
       </c>
       <c r="R20" t="n">
-        <v>7024730</v>
+        <v>7024788</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3095,6 +3057,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3124,16 +3091,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152735</v>
+        <v>135152674</v>
       </c>
       <c r="B21" t="n">
-        <v>108357</v>
+        <v>99291</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3141,28 +3108,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220102</v>
+        <v>221952</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3173,10 +3140,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491933</v>
+        <v>491994</v>
       </c>
       <c r="R21" t="n">
-        <v>7024735</v>
+        <v>7024761</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3240,16 +3207,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152646</v>
+        <v>135152795</v>
       </c>
       <c r="B22" t="n">
-        <v>106391</v>
+        <v>101478</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3257,28 +3224,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221725</v>
+        <v>222498</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3289,10 +3256,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>491996</v>
+        <v>492072</v>
       </c>
       <c r="R22" t="n">
-        <v>7024788</v>
+        <v>7024744</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3327,11 +3294,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3361,16 +3323,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152674</v>
+        <v>135152799</v>
       </c>
       <c r="B23" t="n">
-        <v>99291</v>
+        <v>101478</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3378,21 +3340,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221952</v>
+        <v>222498</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3410,10 +3372,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491994</v>
+        <v>491940</v>
       </c>
       <c r="R23" t="n">
-        <v>7024761</v>
+        <v>7024802</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3477,13 +3439,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152795</v>
+        <v>135152803</v>
       </c>
       <c r="B24" t="n">
         <v>101478</v>
@@ -3526,10 +3488,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492072</v>
+        <v>492030</v>
       </c>
       <c r="R24" t="n">
-        <v>7024744</v>
+        <v>7024798</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3593,13 +3555,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152799</v>
+        <v>135152814</v>
       </c>
       <c r="B25" t="n">
         <v>101478</v>
@@ -3642,10 +3604,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>491940</v>
+        <v>492106</v>
       </c>
       <c r="R25" t="n">
-        <v>7024802</v>
+        <v>7024668</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3709,16 +3671,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152803</v>
+        <v>135152780</v>
       </c>
       <c r="B26" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3726,21 +3688,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3758,10 +3720,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492030</v>
+        <v>492108</v>
       </c>
       <c r="R26" t="n">
-        <v>7024798</v>
+        <v>7024715</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3796,6 +3758,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3808,7 +3775,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3825,16 +3792,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152814</v>
+        <v>135152781</v>
       </c>
       <c r="B27" t="n">
-        <v>101478</v>
+        <v>98285</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3842,21 +3809,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222498</v>
+        <v>222741</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3874,10 +3841,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>492106</v>
+        <v>491956</v>
       </c>
       <c r="R27" t="n">
-        <v>7024668</v>
+        <v>7024753</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3927,6 +3894,11 @@
           <t>Granskog</t>
         </is>
       </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3941,13 +3913,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152780</v>
+        <v>135152782</v>
       </c>
       <c r="B28" t="n">
         <v>98285</v>
@@ -3990,10 +3962,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492108</v>
+        <v>492020</v>
       </c>
       <c r="R28" t="n">
-        <v>7024715</v>
+        <v>7024753</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4028,11 +4000,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4045,7 +4012,12 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4062,13 +4034,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152781</v>
+        <v>135152783</v>
       </c>
       <c r="B29" t="n">
         <v>98285</v>
@@ -4111,10 +4083,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>491956</v>
+        <v>492059</v>
       </c>
       <c r="R29" t="n">
-        <v>7024753</v>
+        <v>7024724</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4183,16 +4155,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135152782</v>
+        <v>135471205</v>
       </c>
       <c r="B30" t="n">
-        <v>98285</v>
+        <v>98309</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4217,8 +4189,16 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4228,14 +4208,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492020</v>
+        <v>492009</v>
       </c>
       <c r="R30" t="n">
-        <v>7024753</v>
+        <v>7024701</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4262,12 +4242,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4280,40 +4260,30 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI30" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152783</v>
+        <v>135152665</v>
       </c>
       <c r="B31" t="n">
-        <v>98285</v>
+        <v>101380</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4321,28 +4291,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4353,10 +4323,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492059</v>
+        <v>492004</v>
       </c>
       <c r="R31" t="n">
-        <v>7024724</v>
+        <v>7024816</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4403,7 +4373,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -4425,16 +4395,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135471205</v>
+        <v>135152666</v>
       </c>
       <c r="B32" t="n">
-        <v>98309</v>
+        <v>101380</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4442,50 +4412,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222741</v>
+        <v>222771</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>492009</v>
+        <v>491958</v>
       </c>
       <c r="R32" t="n">
-        <v>7024701</v>
+        <v>7024801</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4512,12 +4474,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4530,30 +4492,35 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152665</v>
+        <v>135152684</v>
       </c>
       <c r="B33" t="n">
-        <v>101380</v>
+        <v>99075</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4561,16 +4528,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>222771</v>
+        <v>223049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4593,10 +4560,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492004</v>
+        <v>492050</v>
       </c>
       <c r="R33" t="n">
-        <v>7024816</v>
+        <v>7024700</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4643,12 +4610,7 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AI33" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4665,16 +4627,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152666</v>
+        <v>135152685</v>
       </c>
       <c r="B34" t="n">
-        <v>101380</v>
+        <v>101368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4682,28 +4644,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>222771</v>
+        <v>224885</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4714,10 +4676,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>491958</v>
+        <v>492048</v>
       </c>
       <c r="R34" t="n">
-        <v>7024801</v>
+        <v>7024654</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4781,16 +4743,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135152685</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152684</v>
+        <v>135152693</v>
       </c>
       <c r="B35" t="n">
-        <v>99075</v>
+        <v>101368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4798,28 +4760,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>223049</v>
+        <v>224885</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Nordisk stormhatt</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Koelle) Korsh.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4830,10 +4792,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492050</v>
+        <v>492089</v>
       </c>
       <c r="R35" t="n">
-        <v>7024700</v>
+        <v>7024769</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4880,7 +4842,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4897,13 +4859,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152693</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152685</v>
+        <v>135152706</v>
       </c>
       <c r="B36" t="n">
         <v>101368</v>
@@ -4935,7 +4897,7 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4946,10 +4908,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>492048</v>
+        <v>491979</v>
       </c>
       <c r="R36" t="n">
-        <v>7024654</v>
+        <v>7024678</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5012,238 +4974,6 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>135152693</v>
-      </c>
-      <c r="B37" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>492089</v>
-      </c>
-      <c r="R37" t="n">
-        <v>7024769</v>
-      </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Högörtgranskog</t>
-        </is>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>135152706</v>
-      </c>
-      <c r="B38" t="n">
-        <v>101368</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E38" t="n">
-        <v>224885</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Nordisk stormhatt</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>(Koelle) Korsh.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
-        </is>
-      </c>
-      <c r="Q38" t="n">
-        <v>491979</v>
-      </c>
-      <c r="R38" t="n">
-        <v>7024678</v>
-      </c>
-      <c r="S38" t="n">
-        <v>10</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Östersund</t>
-        </is>
-      </c>
-      <c r="V38" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>Lit</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="AD38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>Kristian Zackrisson</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5286,8 +5016,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ36"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2014,10 +2014,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135152676</v>
+        <v>135152661</v>
       </c>
       <c r="B12" t="n">
-        <v>58415</v>
+        <v>58006</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2025,21 +2025,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103001</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2069,10 +2069,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>491978</v>
+        <v>491961</v>
       </c>
       <c r="R12" t="n">
-        <v>7024717</v>
+        <v>7024767</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2107,6 +2107,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Synobservation av 1 hane av tretåig hackspett som födosökte på en lutande död gran med 22,5 cm i brösthöjdsdiameter och även andra stående döda granar. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -2119,6 +2124,11 @@
       <c r="AH12" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal.</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2135,16 +2145,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152676</t>
+          <t>https://artportalen.se/Sighting/135152661</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136199553</v>
+        <v>135152663</v>
       </c>
       <c r="B13" t="n">
-        <v>58167</v>
+        <v>58006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2152,21 +2162,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2178,7 +2188,7 @@
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2188,17 +2198,17 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>492073</v>
+        <v>492035</v>
       </c>
       <c r="R13" t="n">
-        <v>7024775</v>
+        <v>7024713</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2222,27 +2232,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>19:38</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
+          <t>Synobservation av 1 individ av tretåig hackspett som födosökte långt upp i en stående död gran med barken kvar intill 1 större hackspett som födosökte i toppen av en avbarkad stående död gran. Möjligen hona men var svårt att riktigt se huvudet då den tretåiga hackspetten satt så långt upp i granen. Därefter hördes även trummning av tretåig hackspett. På fyndplatsen finns stående död ved av gran som indikerar mycket högt livsmiljövärde för tretåig hackspett. I skogsbeståndet där fyndplatsen ligger finns i i stor del av ytan stående död ved som indikerar mestadels högt och mycket högt livsmiljövärde för tretåig hackspett.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2256,7 +2256,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Grandominerad barrskog med inslag av tall, björk, asp, sälg, rönn och gråal. Stor stamdiameter-spridning och bitvis gott om liggande död ved.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2273,59 +2278,71 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136199553</t>
+          <t>https://artportalen.se/Sighting/135152663</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135152777</v>
+        <v>135152676</v>
       </c>
       <c r="B14" t="n">
-        <v>99186</v>
+        <v>58415</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219790</v>
+        <v>103001</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>492109</v>
+        <v>491978</v>
       </c>
       <c r="R14" t="n">
-        <v>7024714</v>
+        <v>7024717</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2360,24 +2377,18 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Flera plantor i blom i ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2394,58 +2405,70 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152777</t>
+          <t>https://artportalen.se/Sighting/135152676</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135471439</v>
+        <v>136199553</v>
       </c>
       <c r="B15" t="n">
-        <v>98314</v>
+        <v>58167</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>219815</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ekbräken</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gymnocarpium dryopteris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Newman</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>491957</v>
+        <v>492073</v>
       </c>
       <c r="R15" t="n">
-        <v>7024690</v>
+        <v>7024775</v>
       </c>
       <c r="S15" t="n">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2469,12 +2492,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>19:38</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>19:38</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 1 talltita, möjligen fler, hördes i ett område med bitvis flerskiktad kalkbarrskog. Avverkning av denna skog har påbörjats av Norra skog utan hänsynsplanering för talltita och utan hänsyn till tretåig hackspett som även lever här (augusti 2026).</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2483,34 +2521,38 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471439</t>
+          <t>https://artportalen.se/Sighting/136199553</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135152656</v>
+        <v>135152777</v>
       </c>
       <c r="B16" t="n">
-        <v>99293</v>
+        <v>99186</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2518,21 +2560,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2553,7 +2595,7 @@
         <v>492109</v>
       </c>
       <c r="R16" t="n">
-        <v>7024713</v>
+        <v>7024714</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2590,7 +2632,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Flera plantor i blomning i ett rikkärr.</t>
+          <t>Flera plantor i blom i ett rikkärr.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2622,16 +2664,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152656</t>
+          <t>https://artportalen.se/Sighting/135152777</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135152736</v>
+        <v>135471439</v>
       </c>
       <c r="B17" t="n">
-        <v>99607</v>
+        <v>98314</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2639,45 +2681,41 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>219880</v>
+        <v>219815</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kransrams</t>
+          <t>Ekbräken</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Polygonatum verticillatum</t>
+          <t>Gymnocarpium dryopteris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) All.</t>
+          <t>(L.) Newman</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>492090</v>
+        <v>491957</v>
       </c>
       <c r="R17" t="n">
-        <v>7024764</v>
+        <v>7024690</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2701,12 +2739,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2719,35 +2757,30 @@
       <c r="AG17" t="b">
         <v>0</v>
       </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152736</t>
+          <t>https://artportalen.se/Sighting/135471439</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135152787</v>
+        <v>135152656</v>
       </c>
       <c r="B18" t="n">
-        <v>108287</v>
+        <v>99293</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2755,28 +2788,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220083</v>
+        <v>219847</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -2787,10 +2820,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>492029</v>
+        <v>492109</v>
       </c>
       <c r="R18" t="n">
-        <v>7024730</v>
+        <v>7024713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2825,6 +2858,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Flera plantor i blomning i ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2837,7 +2875,7 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2854,16 +2892,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152787</t>
+          <t>https://artportalen.se/Sighting/135152656</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135152735</v>
+        <v>135152736</v>
       </c>
       <c r="B19" t="n">
-        <v>108357</v>
+        <v>99607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2871,28 +2909,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220102</v>
+        <v>219880</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
@@ -2903,10 +2941,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>491933</v>
+        <v>492090</v>
       </c>
       <c r="R19" t="n">
-        <v>7024735</v>
+        <v>7024764</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2970,16 +3008,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152735</t>
+          <t>https://artportalen.se/Sighting/135152736</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135152646</v>
+        <v>135152787</v>
       </c>
       <c r="B20" t="n">
-        <v>106391</v>
+        <v>108287</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2987,28 +3025,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221725</v>
+        <v>220083</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
@@ -3019,10 +3057,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>491996</v>
+        <v>492029</v>
       </c>
       <c r="R20" t="n">
-        <v>7024788</v>
+        <v>7024730</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3057,11 +3095,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Överblommad med färsk kapsel.</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -3091,16 +3124,16 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152646</t>
+          <t>https://artportalen.se/Sighting/135152787</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135152674</v>
+        <v>135152735</v>
       </c>
       <c r="B21" t="n">
-        <v>99291</v>
+        <v>108357</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3108,28 +3141,28 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221952</v>
+        <v>220102</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Moench</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
@@ -3140,10 +3173,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>491994</v>
+        <v>491933</v>
       </c>
       <c r="R21" t="n">
-        <v>7024761</v>
+        <v>7024735</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3207,16 +3240,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152674</t>
+          <t>https://artportalen.se/Sighting/135152735</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135152795</v>
+        <v>135152646</v>
       </c>
       <c r="B22" t="n">
-        <v>101478</v>
+        <v>106391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3224,28 +3257,28 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>222498</v>
+        <v>221725</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
@@ -3256,10 +3289,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>492072</v>
+        <v>491996</v>
       </c>
       <c r="R22" t="n">
-        <v>7024744</v>
+        <v>7024788</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3294,6 +3327,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Överblommad med färsk kapsel.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3323,16 +3361,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152795</t>
+          <t>https://artportalen.se/Sighting/135152646</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135152799</v>
+        <v>135152674</v>
       </c>
       <c r="B23" t="n">
-        <v>101478</v>
+        <v>99291</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3340,21 +3378,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3372,10 +3410,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>491940</v>
+        <v>491994</v>
       </c>
       <c r="R23" t="n">
-        <v>7024802</v>
+        <v>7024761</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3439,13 +3477,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152799</t>
+          <t>https://artportalen.se/Sighting/135152674</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135152803</v>
+        <v>135152795</v>
       </c>
       <c r="B24" t="n">
         <v>101478</v>
@@ -3488,10 +3526,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>492030</v>
+        <v>492072</v>
       </c>
       <c r="R24" t="n">
-        <v>7024798</v>
+        <v>7024744</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3555,13 +3593,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152803</t>
+          <t>https://artportalen.se/Sighting/135152795</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135152814</v>
+        <v>135152799</v>
       </c>
       <c r="B25" t="n">
         <v>101478</v>
@@ -3604,10 +3642,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>492106</v>
+        <v>491940</v>
       </c>
       <c r="R25" t="n">
-        <v>7024668</v>
+        <v>7024802</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3671,16 +3709,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152814</t>
+          <t>https://artportalen.se/Sighting/135152799</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135152780</v>
+        <v>135152803</v>
       </c>
       <c r="B26" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3688,21 +3726,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3720,10 +3758,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>492108</v>
+        <v>492030</v>
       </c>
       <c r="R26" t="n">
-        <v>7024715</v>
+        <v>7024798</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3758,11 +3796,6 @@
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gott om finbräken övre delen av ett rikkärr.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3775,7 +3808,7 @@
       </c>
       <c r="AH26" t="inlineStr">
         <is>
-          <t>Rikkärr med barrträd</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3792,16 +3825,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152780</t>
+          <t>https://artportalen.se/Sighting/135152803</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135152781</v>
+        <v>135152814</v>
       </c>
       <c r="B27" t="n">
-        <v>98285</v>
+        <v>101478</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3809,21 +3842,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>222741</v>
+        <v>222498</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3841,10 +3874,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>491956</v>
+        <v>492106</v>
       </c>
       <c r="R27" t="n">
-        <v>7024753</v>
+        <v>7024668</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3894,11 +3927,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI27" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
-        </is>
-      </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
@@ -3913,13 +3941,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152781</t>
+          <t>https://artportalen.se/Sighting/135152814</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135152782</v>
+        <v>135152780</v>
       </c>
       <c r="B28" t="n">
         <v>98285</v>
@@ -3962,10 +3990,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>492020</v>
+        <v>492108</v>
       </c>
       <c r="R28" t="n">
-        <v>7024753</v>
+        <v>7024715</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4000,6 +4028,11 @@
           <t>2026-07-13</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Gott om finbräken övre delen av ett rikkärr.</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -4012,12 +4045,7 @@
       </c>
       <c r="AH28" t="inlineStr">
         <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Kalkgranskog.</t>
+          <t>Rikkärr med barrträd</t>
         </is>
       </c>
       <c r="AT28" t="inlineStr"/>
@@ -4034,13 +4062,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152782</t>
+          <t>https://artportalen.se/Sighting/135152780</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135152783</v>
+        <v>135152781</v>
       </c>
       <c r="B29" t="n">
         <v>98285</v>
@@ -4083,10 +4111,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>492059</v>
+        <v>491956</v>
       </c>
       <c r="R29" t="n">
-        <v>7024724</v>
+        <v>7024753</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4155,16 +4183,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152783</t>
+          <t>https://artportalen.se/Sighting/135152781</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135471205</v>
+        <v>135152782</v>
       </c>
       <c r="B30" t="n">
-        <v>98309</v>
+        <v>98285</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4189,16 +4217,8 @@
           <t>(Lam.) Desv.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
           <t>fullt utvecklade blad</t>
@@ -4208,14 +4228,14 @@
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>492009</v>
+        <v>492020</v>
       </c>
       <c r="R30" t="n">
-        <v>7024701</v>
+        <v>7024753</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4242,12 +4262,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4260,30 +4280,40 @@
       <c r="AG30" t="b">
         <v>0</v>
       </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
+        </is>
+      </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Tomas Lundqvist</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135471205</t>
+          <t>https://artportalen.se/Sighting/135152782</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135152665</v>
+        <v>135152783</v>
       </c>
       <c r="B31" t="n">
-        <v>101380</v>
+        <v>98285</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4291,28 +4321,28 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
@@ -4323,10 +4353,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>492004</v>
+        <v>492059</v>
       </c>
       <c r="R31" t="n">
-        <v>7024816</v>
+        <v>7024724</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4373,7 +4403,7 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
@@ -4395,16 +4425,16 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152665</t>
+          <t>https://artportalen.se/Sighting/135152783</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135152666</v>
+        <v>135471205</v>
       </c>
       <c r="B32" t="n">
-        <v>101380</v>
+        <v>98309</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4412,42 +4442,50 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>i frukt</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+          <t>Kalkbarrskog NO Boda, Boda, Lit, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>491958</v>
+        <v>492009</v>
       </c>
       <c r="R32" t="n">
-        <v>7024801</v>
+        <v>7024701</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4474,12 +4512,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4492,35 +4530,30 @@
       <c r="AG32" t="b">
         <v>0</v>
       </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Tomas Lundqvist</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152666</t>
+          <t>https://artportalen.se/Sighting/135471205</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135152684</v>
+        <v>135152665</v>
       </c>
       <c r="B33" t="n">
-        <v>99075</v>
+        <v>101380</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4528,16 +4561,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223049</v>
+        <v>222771</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ormbär</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Paris quadrifolia</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4560,10 +4593,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>492050</v>
+        <v>492004</v>
       </c>
       <c r="R33" t="n">
-        <v>7024700</v>
+        <v>7024816</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4610,7 +4643,12 @@
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkgranskog.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4627,16 +4665,16 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152684</t>
+          <t>https://artportalen.se/Sighting/135152665</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135152685</v>
+        <v>135152666</v>
       </c>
       <c r="B34" t="n">
-        <v>101368</v>
+        <v>101380</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4644,28 +4682,28 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>224885</v>
+        <v>222771</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -4676,10 +4714,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>492048</v>
+        <v>491958</v>
       </c>
       <c r="R34" t="n">
-        <v>7024654</v>
+        <v>7024801</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4743,16 +4781,16 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152685</t>
+          <t>https://artportalen.se/Sighting/135152666</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135152693</v>
+        <v>135152684</v>
       </c>
       <c r="B35" t="n">
-        <v>101368</v>
+        <v>99075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4760,28 +4798,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>224885</v>
+        <v>223049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Nordisk stormhatt</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Aconitum lycoctonum subsp. septentrionale</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Koelle) Korsh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>i frukt</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -4792,10 +4830,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>492089</v>
+        <v>492050</v>
       </c>
       <c r="R35" t="n">
-        <v>7024769</v>
+        <v>7024700</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4842,7 +4880,7 @@
       </c>
       <c r="AH35" t="inlineStr">
         <is>
-          <t>Högörtgranskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT35" t="inlineStr"/>
@@ -4859,13 +4897,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135152693</t>
+          <t>https://artportalen.se/Sighting/135152684</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135152706</v>
+        <v>135152685</v>
       </c>
       <c r="B36" t="n">
         <v>101368</v>
@@ -4897,7 +4935,7 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
@@ -4908,10 +4946,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>491979</v>
+        <v>492048</v>
       </c>
       <c r="R36" t="n">
-        <v>7024678</v>
+        <v>7024654</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4974,6 +5012,238 @@
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152685</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>135152693</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>492089</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7024769</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Högörtgranskog</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135152693</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>135152706</v>
+      </c>
+      <c r="B38" t="n">
+        <v>101368</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>224885</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Nordisk stormhatt</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Aconitum lycoctonum subsp. septentrionale</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Koelle) Korsh.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog 900 meter nordöst om Boda, Jmt</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>491979</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7024678</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lit</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135152706</t>
         </is>
@@ -5016,6 +5286,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27881-2026 artfynd.xlsx
+++ b/artfynd/A 27881-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136200752</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
